--- a/reports/리워드유지_신청자·이전금액구간_스트레스테스트.xlsx
+++ b/reports/리워드유지_신청자·이전금액구간_스트레스테스트.xlsx
@@ -22,10 +22,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="#,##0.00&quot;배&quot;"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="+0.0;-0.0"/>
+    <numFmt numFmtId="167" formatCode="+0.00;-0.00"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -101,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -118,13 +119,18 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -528,12 +534,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>기준셀(×1.0/+0%)</t>
+          <t>기준셀(×1.0/θ=0)</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>worst case(×1.8/+150%)</t>
+          <t>worst case(×1.8/θ=+1.5)</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -557,16 +563,16 @@
         <v>20930</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>8.67385849915679</v>
+        <v>10.09103267615629</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>26.29088570891144</v>
+        <v>35.69217500430851</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>3.031048490296129</v>
+        <v>3.537019069281599</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>18.51324732502955</v>
+        <v>20.18347392915378</v>
       </c>
     </row>
     <row r="6">
@@ -579,16 +585,16 @@
         <v>26132</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>10.82950180767931</v>
+        <v>12.59887472436967</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>32.82474510482557</v>
+        <v>44.56246015158543</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>3.03104849029613</v>
+        <v>3.537019069281598</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>23.14033891428636</v>
+        <v>25.25812766587075</v>
       </c>
     </row>
     <row r="7">
@@ -601,16 +607,16 @@
         <v>26786</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>11.10063484000036</v>
+        <v>12.91430669608134</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>33.64656247311171</v>
+        <v>45.67814905059073</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>3.03104849029613</v>
+        <v>3.537019069281599</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>23.76442246961729</v>
+        <v>25.96028242180204</v>
       </c>
     </row>
     <row r="8">
@@ -621,16 +627,16 @@
       </c>
       <c r="B8" s="8" t="inlineStr"/>
       <c r="C8" s="9" t="n">
-        <v>30.60399514683645</v>
+        <v>35.60421409660729</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>92.76219328684871</v>
+        <v>125.9327842064847</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>3.03104849029613</v>
+        <v>3.537019069281599</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>57.01954059276672</v>
+        <v>61.26466555480935</v>
       </c>
     </row>
     <row r="10">
@@ -664,11 +670,11 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>30.60399514683645</v>
+        <v>35.60421409660729</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>신청 현 수준 유지 + 구간 믹스 현행유지</t>
+          <t>신청 현 수준 유지 + 금액 구간 믹스 = 실측 10회차 평균</t>
         </is>
       </c>
     </row>
@@ -679,11 +685,11 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>45.16896396660422</v>
+        <v>45.82356405048272</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>배수·시프트 상방 비대칭이 반영된 중앙값</t>
+          <t>배수·기울기 상방 비대칭이 반영된 중앙값</t>
         </is>
       </c>
     </row>
@@ -694,7 +700,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>57.01954059276672</v>
+        <v>61.26466555480935</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
@@ -709,7 +715,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>65.41800870893321</v>
+        <v>71.40188401682657</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
@@ -724,18 +730,18 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>92.76219328684871</v>
+        <v>125.9327842064847</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>결정론 최악 셀(×1.8 신청 × +150% 믹스 상향)</t>
+          <t>결정론 최악 셀(신청 ×1.8 × 믹스 θ=+1.5 = 관측 범위 초과)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>핵심: 리워드를 현재안대로 유지해도 신청자 1.8배 + 대량입금 믹스 상향이 겹치면 예산은 기준 대비 약 3.0배로 늘어난다. 편성 권고는 3회차 합 57.0~65.4억원(P90 범위).</t>
+          <t>핵심: 리워드를 현재안대로 유지해도 신청자 1.8배 + 대량입금 믹스 상향이 겹치면 예산은 기준 대비 약 3.5배로 늘어난다. 편성 권고는 3회차 합 61.3~71.4억원(P90 범위).</t>
         </is>
       </c>
     </row>
@@ -750,7 +756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -815,7 +821,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>32.5% (전환 63.9% × 조건충족 50.8%)</t>
+          <t>21.19% — 실측 금액 분포에서 유도(수관 5백만원 이상 비중)</t>
         </is>
       </c>
     </row>
@@ -841,89 +847,91 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>축2 이전금액 구간 비율</t>
+          <t>축2 수관금액 구간 비율</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>이전금액 분포 중앙값 상향률 +0%, +25%, +50%, +100%, +150% (연말 일시 대량입금 고객 유입 가정)</t>
+          <t>기울기 θ = -1.0, +0.0, +0.5, +1.0, +1.5. θ=0 실측 10회차 평균, θ=+1 관측 최고(1470), θ=-1 관측 최저(1536), |θ|&gt;1 은 관측 범위 외삽</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>[ 당첨자 이전금액 분포 — 실적으로 역산 ]</t>
+          <t>[ 수관금액 구간 분포 — 실측 데이터 ]</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>분포 형태</t>
+          <t>출처</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>로그정규(우측 꼬리) — 소액이 다수, 대액이 소수인 입금 분포에 부합</t>
+          <t>data/transfer_amount_distribution.csv — 이벤트 회차별 타사수관금액 구간 분포</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>앵커 (a) 조건충족률</t>
+          <t>사용 회차</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>51% = P(이전금액 ≥ 5백만원). 최근 실측 당첨/순입금</t>
+          <t>성숙 10회차 단순평균 (회차별 고객 수가 없어 가중평균 불가). 진행 초기라 수관 실적이 안 잡힌 1647 제외</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>앵커 (b) 평균 예산반영 단가</t>
+          <t>구간 내부 보간</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>127,665원. 최근 실측 예산/당첨</t>
+          <t>로그축 균등. 1.5배 인정 때문에 리워드 구간 경계가 실측 구간 안쪽(예: 실제 2,000만원)에 떨어져 쪼개 적분해야 한다. 구간 경계에서는 실측치를 정확히 재현</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>역산 결과 sigma</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="n">
-        <v>1.6195</v>
+          <t>대상자 평균 수관금액</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>5,493만원</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>당첨자 평균 이전금액</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>3,600만원</t>
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>치환 효과</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>이전(로그정규 가정) 지급률 32.5%×단가 12.8만원 = 41,442원/신청 → 실측 21.19%×22.7만원 = 48,213원/신청 (+16.3%)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>검증</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>구간표·1.5배 인정·제세 규칙을 모두 적용한 모델이 최근 실측 단가를 그대로 재현 → 기준선 정합성 확인</t>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>해석</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>분해는 크게 달라졌지만(대상자 적고 단가 높음) 곱인 신청 1인당 예산은 수렴한다 — 두 방식이 같은 총예산을 다르게 쪼개고 있었다는 뜻</t>
         </is>
       </c>
     </row>
@@ -963,6 +971,22 @@
       <c r="B25" s="4" t="inlineStr">
         <is>
           <t>몬테카를로 P50이 기준셀보다 높은 것은 정상이다. 두 축 모두 최빈값에서 위쪽으로 더 멀리 뻗은 삼각분포라 중앙값이 최빈값 위에 형성된다(상방 비대칭 설정의 귀결).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr"/>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>연말효과 가정은 실측과 어긋난다. 유일한 12월 단독 회차 1536(202512)이 10회차 중 최저이고 최고는 9월 회차 1470(202509)이다. 축2 상향은 계절 효과가 아니라 일반적인 상방 리스크로 읽어야 한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr"/>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>최저 구간 [0, 5백만)의 하한은 10만원으로 가정했다(로그축 보간용). 대상자 평균 수관금액 계산에만 영향을 준다.</t>
         </is>
       </c>
     </row>
@@ -1013,17 +1037,17 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>실제 이전금액 하한</t>
+          <t>실제 수관금액 하한</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>실제 이전금액 상한</t>
+          <t>실제 수관금액 상한</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>기준 구간비율</t>
+          <t>대상자 중 비율(실측)</t>
         </is>
       </c>
     </row>
@@ -1045,8 +1069,8 @@
       <c r="E4" s="5" t="n">
         <v>10000000</v>
       </c>
-      <c r="F4" s="14" t="n">
-        <v>0.3264668889423492</v>
+      <c r="F4" s="13" t="n">
+        <v>0.05615856536101956</v>
       </c>
     </row>
     <row r="5">
@@ -1067,8 +1091,8 @@
       <c r="E5" s="5" t="n">
         <v>20000000</v>
       </c>
-      <c r="F5" s="14" t="n">
-        <v>0.2754742723029229</v>
+      <c r="F5" s="13" t="n">
+        <v>0.1473856668324076</v>
       </c>
     </row>
     <row r="6">
@@ -1089,8 +1113,8 @@
       <c r="E6" s="5" t="n">
         <v>33333333.33333333</v>
       </c>
-      <c r="F6" s="14" t="n">
-        <v>0.1513364318800685</v>
+      <c r="F6" s="13" t="n">
+        <v>0.1346885012625715</v>
       </c>
     </row>
     <row r="7">
@@ -1111,8 +1135,8 @@
       <c r="E7" s="5" t="n">
         <v>66666666.66666666</v>
       </c>
-      <c r="F7" s="14" t="n">
-        <v>0.1335736729436297</v>
+      <c r="F7" s="13" t="n">
+        <v>0.3463687764125888</v>
       </c>
     </row>
     <row r="8">
@@ -1133,8 +1157,8 @@
       <c r="E8" s="5" t="n">
         <v>133333333.3333333</v>
       </c>
-      <c r="F8" s="14" t="n">
-        <v>0.06878578501099909</v>
+      <c r="F8" s="13" t="n">
+        <v>0.2614966200826097</v>
       </c>
     </row>
     <row r="9">
@@ -1155,8 +1179,8 @@
       <c r="E9" s="5" t="n">
         <v>200000000</v>
       </c>
-      <c r="F9" s="14" t="n">
-        <v>0.02055975510257649</v>
+      <c r="F9" s="13" t="n">
+        <v>0.05107034574488645</v>
       </c>
     </row>
     <row r="10">
@@ -1179,8 +1203,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="14" t="n">
-        <v>0.02380319381745404</v>
+      <c r="F10" s="13" t="n">
+        <v>0.002831524303917367</v>
       </c>
     </row>
     <row r="11">
@@ -1189,15 +1213,15 @@
           <t>가중평균</t>
         </is>
       </c>
-      <c r="B11" s="15" t="n">
-        <v>103439</v>
-      </c>
-      <c r="C11" s="15" t="n">
-        <v>127665</v>
+      <c r="B11" s="14" t="n">
+        <v>178978</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>227479</v>
       </c>
       <c r="D11" s="8" t="inlineStr"/>
       <c r="E11" s="8" t="inlineStr"/>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="15" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1226,34 +1250,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>축2 — 타사이전금액 구간 비율 변동 (연말 대량입금 유입 가정)</t>
+          <t>축2 — 수관금액 구간 비율 변동 (실측 회차 변동 방향을 눈금으로)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>시프트</t>
+          <t>기울기 θ</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -1263,269 +1289,572 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>지급률</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>5백만~1천만</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>1천만~3천만</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>3천만~5천만</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>5천만~1억</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>1억~2억</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>2억~3억</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>3억 이상</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>평균 예산반영 단가(원)</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>신청 1인당(원)</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>기준대비</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>당첨자 평균 이전금액(만원)</t>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>대상자 평균 수관금액(만원)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>+0%</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>현행유지</t>
-        </is>
-      </c>
-      <c r="C4" s="14" t="n">
-        <v>0.3264668889423492</v>
-      </c>
-      <c r="D4" s="14" t="n">
-        <v>0.2754742723029229</v>
-      </c>
-      <c r="E4" s="14" t="n">
-        <v>0.1513364318800685</v>
-      </c>
-      <c r="F4" s="14" t="n">
-        <v>0.1335736729436297</v>
-      </c>
-      <c r="G4" s="14" t="n">
-        <v>0.06878578501099909</v>
-      </c>
-      <c r="H4" s="14" t="n">
-        <v>0.02055975510257649</v>
-      </c>
-      <c r="I4" s="14" t="n">
-        <v>0.02380319381745404</v>
-      </c>
-      <c r="J4" s="5" t="n">
-        <v>127665</v>
-      </c>
-      <c r="K4" s="7" t="n">
+      <c r="A4" s="16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>관측최저</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>0.1370000017260002</v>
+      </c>
+      <c r="D4" s="13" t="n">
+        <v>0.06569342969790574</v>
+      </c>
+      <c r="E4" s="13" t="n">
+        <v>0.1796077374457759</v>
+      </c>
+      <c r="F4" s="13" t="n">
+        <v>0.1547457351213028</v>
+      </c>
+      <c r="G4" s="13" t="n">
+        <v>0.3305496196739464</v>
+      </c>
+      <c r="H4" s="13" t="n">
+        <v>0.2267054713324864</v>
+      </c>
+      <c r="I4" s="13" t="n">
+        <v>0.04269799213004082</v>
+      </c>
+      <c r="J4" s="13" t="n">
+        <v>1.459853954919018e-08</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>204008</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>27949</v>
+      </c>
+      <c r="M4" s="7" t="n">
+        <v>0.5797062855471036</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>4984</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>실측평균</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>0.2119423884776955</v>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>0.05615856536101956</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>0.1473856668324076</v>
+      </c>
+      <c r="F5" s="13" t="n">
+        <v>0.1346885012625715</v>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>0.3463687764125888</v>
+      </c>
+      <c r="H5" s="13" t="n">
+        <v>0.2614966200826097</v>
+      </c>
+      <c r="I5" s="13" t="n">
+        <v>0.05107034574488645</v>
+      </c>
+      <c r="J5" s="13" t="n">
+        <v>0.002831524303917367</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>227479</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>48213</v>
+      </c>
+      <c r="M5" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="L4" s="5" t="n">
-        <v>3600</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>+25%</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>완만</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="n">
-        <v>0.2996945073589335</v>
-      </c>
-      <c r="D5" s="14" t="n">
-        <v>0.2680050871610697</v>
-      </c>
-      <c r="E5" s="14" t="n">
-        <v>0.1549853580391489</v>
-      </c>
-      <c r="F5" s="14" t="n">
-        <v>0.1437466894106484</v>
-      </c>
-      <c r="G5" s="14" t="n">
-        <v>0.07845226379692619</v>
-      </c>
-      <c r="H5" s="14" t="n">
-        <v>0.02462229230950981</v>
-      </c>
-      <c r="I5" s="14" t="n">
-        <v>0.03049380192376343</v>
-      </c>
-      <c r="J5" s="5" t="n">
-        <v>144488</v>
-      </c>
-      <c r="K5" s="7" t="n">
-        <v>1.131777924161673</v>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v>4118</v>
+      <c r="N5" s="5" t="n">
+        <v>5493</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>+50%</t>
-        </is>
+      <c r="A6" s="16" t="n">
+        <v>0.5</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>중간</t>
-        </is>
-      </c>
-      <c r="C6" s="14" t="n">
-        <v>0.2779521996009325</v>
-      </c>
-      <c r="D6" s="14" t="n">
-        <v>0.2606407602177366</v>
-      </c>
-      <c r="E6" s="14" t="n">
-        <v>0.1571650680690593</v>
-      </c>
-      <c r="F6" s="14" t="n">
-        <v>0.1518083081251128</v>
-      </c>
-      <c r="G6" s="14" t="n">
-        <v>0.08687931874241339</v>
-      </c>
-      <c r="H6" s="14" t="n">
-        <v>0.02837298763904095</v>
-      </c>
-      <c r="I6" s="14" t="n">
-        <v>0.03718135760570439</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>160177</v>
-      </c>
-      <c r="K6" s="7" t="n">
-        <v>1.25466733495548</v>
+          <t>중간상향</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>0.2601515201290148</v>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>0.0567388134088113</v>
+      </c>
+      <c r="E6" s="13" t="n">
+        <v>0.1276249157796092</v>
+      </c>
+      <c r="F6" s="13" t="n">
+        <v>0.1231965151047397</v>
+      </c>
+      <c r="G6" s="13" t="n">
+        <v>0.3593908980344281</v>
+      </c>
+      <c r="H6" s="13" t="n">
+        <v>0.2805187531508026</v>
+      </c>
+      <c r="I6" s="13" t="n">
+        <v>0.05252709770877667</v>
+      </c>
+      <c r="J6" s="13" t="n">
+        <v>3.006812833356627e-06</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>233131</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>4626</v>
+        <v>60649</v>
+      </c>
+      <c r="M6" s="7" t="n">
+        <v>1.257960709514796</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>5626</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>+100%</t>
-        </is>
+      <c r="A7" s="16" t="n">
+        <v>1</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>강함</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="n">
-        <v>0.2441623348285982</v>
-      </c>
-      <c r="D7" s="14" t="n">
-        <v>0.2467559710939561</v>
-      </c>
-      <c r="E7" s="14" t="n">
-        <v>0.1589160969848493</v>
-      </c>
-      <c r="F7" s="14" t="n">
-        <v>0.1636835091349849</v>
-      </c>
-      <c r="G7" s="14" t="n">
-        <v>0.100960013086082</v>
-      </c>
-      <c r="H7" s="14" t="n">
-        <v>0.03509721229951488</v>
-      </c>
-      <c r="I7" s="14" t="n">
-        <v>0.05042486257201457</v>
-      </c>
-      <c r="J7" s="5" t="n">
-        <v>188931</v>
-      </c>
-      <c r="K7" s="7" t="n">
-        <v>1.479898861788156</v>
+          <t>관측최고</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="n">
+        <v>0.3170000013660002</v>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>0.05678233402660996</v>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>0.1094673067113423</v>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>0.1121822047828263</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>0.3698971327178932</v>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>0.2981570961654739</v>
+      </c>
+      <c r="I7" s="13" t="n">
+        <v>0.05351391928670561</v>
+      </c>
+      <c r="J7" s="13" t="n">
+        <v>6.309148059362271e-09</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>241118</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>5619</v>
+        <v>76434</v>
+      </c>
+      <c r="M7" s="7" t="n">
+        <v>1.585365872494873</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>5799</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>+150%</t>
-        </is>
+      <c r="A8" s="16" t="n">
+        <v>1.5</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>극단</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="n">
-        <v>0.2186358101792761</v>
-      </c>
-      <c r="D8" s="14" t="n">
-        <v>0.2341705559362336</v>
-      </c>
-      <c r="E8" s="14" t="n">
-        <v>0.1586867526477869</v>
-      </c>
-      <c r="F8" s="14" t="n">
-        <v>0.1718228338679895</v>
-      </c>
-      <c r="G8" s="14" t="n">
-        <v>0.1123185155107629</v>
-      </c>
-      <c r="H8" s="14" t="n">
-        <v>0.04097601919583793</v>
-      </c>
-      <c r="I8" s="14" t="n">
-        <v>0.06338951266211301</v>
-      </c>
-      <c r="J8" s="5" t="n">
-        <v>214977</v>
-      </c>
-      <c r="K8" s="7" t="n">
-        <v>1.683915827942294</v>
+          <t>범위초과</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>0.3813403588857868</v>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>0.05647793198057001</v>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>0.09331811386919239</v>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>0.1020534875082248</v>
+      </c>
+      <c r="G8" s="13" t="n">
+        <v>0.3789179506227197</v>
+      </c>
+      <c r="H8" s="13" t="n">
+        <v>0.3150470655109336</v>
+      </c>
+      <c r="I8" s="13" t="n">
+        <v>0.0541854479536162</v>
+      </c>
+      <c r="J8" s="13" t="n">
+        <v>2.554742936564946e-09</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>248434</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>6595</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>※ 시프트는 이전금액 분포의 중앙값 상향률. 상향된 분포를 구간 경계로 다시 적분하므로 구간 비율 합계는 항상 100%다.</t>
+        <v>94738</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <v>1.965010594045332</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>5958</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>※ θ=0 은 실측 10회차 평균, θ=+1 은 관측 최고 회차(1470), θ=-1 은 관측 최저 회차(1536). |θ|&gt;1 은 관측 범위를 벗어난 외삽 구간이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>※ 회차 간 변동은 대상자 내부 믹스가 아니라 '지급률'에 거의 전부 몰려 있다(단가 20.4~24.1만원 ±9% vs 지급률 13.7~31.7% ±40%). 그래서 축2는 금액축을 미는 대신 관측된 변동 방향을 그대로 기울기로 쓴다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>[ 회차별 실측 분포 — 가정 없이 관측치 그대로 ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>회차</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>지급률</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>평균 단가(원)</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>신청 1인당(원)</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>평균 대비</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>등가 θ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>1536</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="C16" s="20" t="n">
+        <v>204008</v>
+      </c>
+      <c r="D16" s="20" t="n">
+        <v>27949</v>
+      </c>
+      <c r="E16" s="21" t="n">
+        <v>0.5797062335231654</v>
+      </c>
+      <c r="F16" s="22" t="n">
+        <v>-1.000000164998106</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>1501</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="n">
+        <v>0.1679999999999999</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>217312</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>36508</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>0.7572403530657924</v>
+      </c>
+      <c r="F17" s="23" t="n">
+        <v>-0.5031608307252122</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>1559</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="n">
+        <v>0.1779999999999999</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>222907</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>39678</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>0.8229716711714284</v>
+      </c>
+      <c r="F18" s="23" t="n">
+        <v>-0.3458549672009231</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>1312</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="n">
+        <v>0.2070000000000001</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>203971</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>42222</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>0.8757498407450347</v>
+      </c>
+      <c r="F19" s="23" t="n">
+        <v>-0.2283583257726709</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>1581</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>232954</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>45426</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>0.9422051528176612</v>
+      </c>
+      <c r="F20" s="23" t="n">
+        <v>-0.09470431495302611</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>1432</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>229158</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>50873</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>1.055181958945496</v>
+      </c>
+      <c r="F21" s="23" t="n">
+        <v>0.1338564785626885</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>1607</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>232586</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>52797</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>1.095089508805191</v>
+      </c>
+      <c r="F22" s="23" t="n">
+        <v>0.2123249580211938</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>1439</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>235344</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>54835</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>1.137365392513166</v>
+      </c>
+      <c r="F23" s="23" t="n">
+        <v>0.2907362583363667</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>1377</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>233357</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>55306</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>1.147124065930766</v>
+      </c>
+      <c r="F24" s="23" t="n">
+        <v>0.3083772101386267</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>1470</t>
+        </is>
+      </c>
+      <c r="B25" s="19" t="n">
+        <v>0.3170000000000001</v>
+      </c>
+      <c r="C25" s="20" t="n">
+        <v>241118</v>
+      </c>
+      <c r="D25" s="20" t="n">
+        <v>76434</v>
+      </c>
+      <c r="E25" s="21" t="n">
+        <v>1.585365822482256</v>
+      </c>
+      <c r="F25" s="22" t="n">
+        <v>0.9999999294263109</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>※ 연말효과 가정과 실측이 어긋난다. 유일한 12월 단독 회차 1536(202512)이 최저이고, 최고는 9월 회차 1470(202509)이다.</t>
         </is>
       </c>
     </row>
@@ -1573,27 +1902,27 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>+0% 현행유지</t>
+          <t>θ=-1.0 관측최저</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>+25% 완만</t>
+          <t>θ=+0.0 실측평균</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>+50% 중간</t>
+          <t>θ=+0.5 중간상향</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>+100% 강함</t>
+          <t>θ=+1.0 관측최고</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>+150% 극단</t>
+          <t>θ=+1.5 범위초과</t>
         </is>
       </c>
     </row>
@@ -1604,19 +1933,19 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>6.939086799325431</v>
+        <v>4.679868056023208</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>7.853505253318207</v>
+        <v>8.072826140925031</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>8.706245541534393</v>
+        <v>10.15529810002764</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>10.26914665617093</v>
+        <v>12.79838305840703</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>11.68483809284953</v>
+        <v>15.86318889080378</v>
       </c>
     </row>
     <row r="6">
@@ -1626,19 +1955,19 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>7.806472649241109</v>
+        <v>5.26485156302611</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>8.835193409982981</v>
+        <v>9.08192940854066</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>9.794526234226192</v>
+        <v>11.4247103625311</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>11.55278998819229</v>
+        <v>14.39818094070791</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>13.14544285445572</v>
+        <v>17.84608750215425</v>
       </c>
     </row>
     <row r="7">
@@ -1647,20 +1976,20 @@
           <t>×1.0 유지</t>
         </is>
       </c>
-      <c r="B7" s="17" t="n">
-        <v>8.67385849915679</v>
+      <c r="B7" s="24" t="n">
+        <v>5.849835070029011</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>9.816881566647757</v>
+        <v>10.09103267615629</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>10.88280692691799</v>
+        <v>12.69412262503456</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>12.83643332021366</v>
+        <v>15.99797882300879</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>14.60604761606191</v>
+        <v>19.82898611350473</v>
       </c>
     </row>
     <row r="8">
@@ -1670,19 +1999,19 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>10.40863019898815</v>
+        <v>7.019802084034811</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>11.78025787997731</v>
+        <v>12.10923921138754</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>13.05936831230159</v>
+        <v>15.23294715004147</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>15.40371998425638</v>
+        <v>19.19757458761055</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>17.52725713927429</v>
+        <v>23.79478333620566</v>
       </c>
     </row>
     <row r="9">
@@ -1692,19 +2021,19 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>13.01078774873518</v>
+        <v>8.774752605043513</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>14.72532234997164</v>
+        <v>15.13654901423443</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>16.32421039037698</v>
+        <v>19.04118393755184</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>19.25464998032048</v>
+        <v>23.99696823451319</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>21.90907142409286</v>
+        <v>29.74347917025709</v>
       </c>
     </row>
     <row r="10">
@@ -1714,25 +2043,25 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>15.61294529848222</v>
+        <v>10.52970312605222</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>17.67038681996596</v>
+        <v>18.16385881708132</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>19.58905246845238</v>
+        <v>22.8494207250622</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>23.10557997638458</v>
-      </c>
-      <c r="F10" s="18" t="n">
-        <v>26.29088570891144</v>
+        <v>28.79636188141582</v>
+      </c>
+      <c r="F10" s="25" t="n">
+        <v>35.69217500430851</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>기준셀 8.67억 → worst 26.29억 (×3.03) · 기준 당첨 6,794명</t>
+          <t>기준셀 10.09억 → worst 35.69억 (×3.54) · 기준 당첨 4,436명</t>
         </is>
       </c>
     </row>
@@ -1751,27 +2080,27 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>+0% 현행유지</t>
+          <t>θ=-1.0 관측최저</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>+25% 완만</t>
+          <t>θ=+0.0 실측평균</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>+50% 중간</t>
+          <t>θ=+0.5 중간상향</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>+100% 강함</t>
+          <t>θ=+1.0 관측최고</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>+150% 극단</t>
+          <t>θ=+1.5 범위초과</t>
         </is>
       </c>
     </row>
@@ -1782,19 +2111,19 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>8.663601446143446</v>
+        <v>5.842917494830102</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>9.805272860480299</v>
+        <v>10.07909977949573</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>10.86993773754924</v>
+        <v>12.67911150988488</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>12.82125391913391</v>
+        <v>15.97906081588313</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>14.5887756021447</v>
+        <v>19.80553784514908</v>
       </c>
     </row>
     <row r="17">
@@ -1804,19 +2133,19 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>9.746551626911375</v>
+        <v>6.573282181683864</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>11.03093196804033</v>
+        <v>11.3389872519327</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>12.22867995474289</v>
+        <v>14.26400044862049</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>14.42391065902564</v>
+        <v>17.97644341786853</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>16.41237255241278</v>
+        <v>22.28123007579272</v>
       </c>
     </row>
     <row r="18">
@@ -1825,20 +2154,20 @@
           <t>×1.0 유지</t>
         </is>
       </c>
-      <c r="B18" s="17" t="n">
-        <v>10.82950180767931</v>
+      <c r="B18" s="24" t="n">
+        <v>7.303646868537626</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>12.25659107560037</v>
+        <v>12.59887472436967</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>13.58742217193655</v>
+        <v>15.84888938735609</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>16.02656739891738</v>
+        <v>19.97382601985392</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>18.23596950268087</v>
+        <v>24.75692230643635</v>
       </c>
     </row>
     <row r="19">
@@ -1848,19 +2177,19 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>12.99540216921517</v>
+        <v>8.764376242245152</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>14.70790929072045</v>
+        <v>15.1186496692436</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>16.30490660632386</v>
+        <v>19.01866726482731</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>19.23188087870086</v>
+        <v>23.96859122382471</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>21.88316340321704</v>
+        <v>29.70830676772363</v>
       </c>
     </row>
     <row r="20">
@@ -1870,19 +2199,19 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>16.24425271151896</v>
+        <v>10.95547030280644</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>18.38488661340056</v>
+        <v>18.8983120865545</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>20.38113325790483</v>
+        <v>23.77333408103414</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>24.03985109837607</v>
+        <v>29.96073902978088</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>27.35395425402131</v>
+        <v>37.13538345965453</v>
       </c>
     </row>
     <row r="21">
@@ -1892,25 +2221,25 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>19.49310325382275</v>
+        <v>13.14656436336773</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>22.06186393608067</v>
+        <v>22.67797450386539</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>24.45735990948579</v>
+        <v>28.52800089724098</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>28.84782131805128</v>
-      </c>
-      <c r="F21" s="18" t="n">
-        <v>32.82474510482557</v>
+        <v>35.95288683573705</v>
+      </c>
+      <c r="F21" s="25" t="n">
+        <v>44.56246015158543</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>기준셀 10.83억 → worst 32.82억 (×3.03) · 기준 당첨 8,483명</t>
+          <t>기준셀 12.60억 → worst 44.56억 (×3.54) · 기준 당첨 5,538명</t>
         </is>
       </c>
     </row>
@@ -1929,27 +2258,27 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>+0% 현행유지</t>
+          <t>θ=-1.0 관측최저</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>+25% 완만</t>
+          <t>θ=+0.0 실측평균</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>+50% 중간</t>
+          <t>θ=+0.5 중간상향</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>+100% 강함</t>
+          <t>θ=+1.0 관측최고</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>+150% 극단</t>
+          <t>θ=+1.5 범위초과</t>
         </is>
       </c>
     </row>
@@ -1960,19 +2289,19 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>8.880507872000289</v>
+        <v>5.98920381216112</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>10.05076276487389</v>
+        <v>10.33144535686507</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>11.14208314481377</v>
+        <v>12.99655233143533</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>13.14225349187398</v>
+        <v>16.3791208823195</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>14.95402776582743</v>
+        <v>20.30139957804032</v>
       </c>
     </row>
     <row r="28">
@@ -1982,19 +2311,19 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>9.990571356000324</v>
+        <v>6.737854288681261</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>11.30710811048312</v>
+        <v>11.62287602647321</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>12.53484353791549</v>
+        <v>14.62112137286475</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>14.78503517835823</v>
+        <v>18.42651099260944</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>16.82328123655585</v>
+        <v>22.83907452529536</v>
       </c>
     </row>
     <row r="29">
@@ -2003,20 +2332,20 @@
           <t>×1.0 유지</t>
         </is>
       </c>
-      <c r="B29" s="17" t="n">
-        <v>11.10063484000036</v>
+      <c r="B29" s="24" t="n">
+        <v>7.486504765201401</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>12.56345345609235</v>
+        <v>12.91430669608134</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>13.9276039310172</v>
+        <v>16.24569041429416</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>16.42781686484248</v>
+        <v>20.47390110289938</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>18.69253470728428</v>
+        <v>25.3767494725504</v>
       </c>
     </row>
     <row r="30">
@@ -2026,19 +2355,19 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>13.32076180800043</v>
+        <v>8.98380571824168</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>15.07614414731082</v>
+        <v>15.49716803529761</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>16.71312471722064</v>
+        <v>19.49482849715299</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>19.71338023781097</v>
+        <v>24.56868132347925</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>22.43104164874113</v>
+        <v>30.45209936706048</v>
       </c>
     </row>
     <row r="31">
@@ -2048,19 +2377,19 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>16.65095226000054</v>
+        <v>11.2297571478021</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>18.84518018413853</v>
+        <v>19.37146004412201</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>20.89140589652581</v>
+        <v>24.36853562144125</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>24.64172529726372</v>
+        <v>30.71085165434907</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>28.03880206092642</v>
+        <v>38.06512420882561</v>
       </c>
     </row>
     <row r="32">
@@ -2070,32 +2399,32 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>19.98114271200065</v>
+        <v>13.47570857736252</v>
       </c>
       <c r="C32" s="6" t="n">
-        <v>22.61421622096625</v>
+        <v>23.24575205294641</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>25.06968707583097</v>
+        <v>29.2422427457295</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>29.57007035671646</v>
-      </c>
-      <c r="F32" s="18" t="n">
-        <v>33.64656247311171</v>
+        <v>36.85302198521888</v>
+      </c>
+      <c r="F32" s="25" t="n">
+        <v>45.67814905059073</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>기준셀 11.10억 → worst 33.65억 (×3.03) · 기준 당첨 8,695명</t>
+          <t>기준셀 12.91억 → worst 45.68억 (×3.54) · 기준 당첨 5,677명</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>※ 연두색=기준셀(신청 유지·믹스 현행유지), 주황색=worst case.</t>
+          <t>※ 연두색=기준셀(신청 유지 · 믹스 = 실측 10회차 평균), 주황색=worst case.</t>
         </is>
       </c>
     </row>
@@ -2131,14 +2460,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>방법: 40,000회 시뮬레이션. 신청배수 삼각(0.8/1.0/1.8), 믹스 시프트 삼각(0/0/+150%), 지급률 Beta(평균 32.5%, CV 0.22).</t>
+          <t>방법: 40,000회 시뮬레이션. 신청배수 삼각(0.8/1.0/1.8), 믹스 기울기 삼각(θ=-1.0/0/+1.5), 지급률은 기울기에서 유도 후 잔여 잡음 CV 0.22.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>시프트 최빈값을 0으로 두어 '상향은 상방 리스크'라는 비대칭을 반영했다.</t>
+          <t>기울기 밴드는 실측 관측 범위에서 왔고 최빈값은 10회차 평균(θ=0)이다 — 임의 가정이 아니라 데이터가 눈금이다.</t>
         </is>
       </c>
     </row>
@@ -2181,19 +2510,19 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>12.98331779541588</v>
+        <v>13.29292930093409</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>12.41336484228074</v>
+        <v>12.34570939074941</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>18.51324732502955</v>
+        <v>20.18347392915378</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>20.6329947287504</v>
+        <v>23.20413553632055</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>24.93971532302237</v>
+        <v>29.52343428917947</v>
       </c>
     </row>
     <row r="8">
@@ -2203,19 +2532,19 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>16.21922587050891</v>
+        <v>16.61576465122281</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>15.51836068691492</v>
+        <v>15.49487155787047</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>23.14033891428636</v>
+        <v>25.25812766587075</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>25.76875858484826</v>
+        <v>28.92249157834407</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>30.89758520016531</v>
+        <v>36.75031915341793</v>
       </c>
     </row>
     <row r="9">
@@ -2225,19 +2554,19 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>16.60431415811143</v>
+        <v>17.058942493138</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>15.8569485842614</v>
+        <v>15.84496873698965</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>23.76442246961729</v>
+        <v>25.96028242180204</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>26.4098733449349</v>
+        <v>29.86600331114009</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>32.2283357445135</v>
+        <v>38.34256687908064</v>
       </c>
     </row>
     <row r="10">
@@ -2247,19 +2576,19 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>45.80685782403621</v>
+        <v>46.96763644529489</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>45.16896396660422</v>
+        <v>45.82356405048272</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>57.01954059276672</v>
+        <v>61.26466555480935</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>60.83590780152173</v>
+        <v>66.432120045487</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>68.19539889693337</v>
+        <v>76.78500243787725</v>
       </c>
     </row>
     <row r="11">
@@ -2270,18 +2599,18 @@
       </c>
       <c r="B11" s="12" t="inlineStr"/>
       <c r="C11" s="12" t="inlineStr"/>
-      <c r="D11" s="18" t="n">
-        <v>65.41800870893321</v>
-      </c>
-      <c r="E11" s="18" t="n">
-        <v>72.81162665853357</v>
+      <c r="D11" s="25" t="n">
+        <v>71.40188401682657</v>
+      </c>
+      <c r="E11" s="25" t="n">
+        <v>81.99263042580471</v>
       </c>
       <c r="F11" s="12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>※ 합산 P90은 회차별 충격이 독립이면 57.0억(분산효과 최대), 모든 회차가 함께 움직이면 65.4억이다. 실제 편성치는 그 사이이며, 연말 대량입금처럼 회차를 가로지르는 충격을 크게 볼수록 상단에 가깝다.</t>
+          <t>※ 합산 P90은 회차별 충격이 독립이면 61.3억(분산효과 최대), 모든 회차가 함께 움직이면 71.4억이다. 실제 편성치는 그 사이이며, 연말 대량입금처럼 회차를 가로지르는 충격을 크게 볼수록 상단에 가깝다.</t>
         </is>
       </c>
     </row>
@@ -2303,16 +2632,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2340,20 +2670,25 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>지급률</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>당첨자</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>평균 단가(원)</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>총예산(억)</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>누적 배율</t>
         </is>
@@ -2367,22 +2702,25 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>① 기준 (신청 유지 · 믹스 현행유지)</t>
+          <t>① 기준 (신청 유지 · 믹스 = 실측 10회차 평균)</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
         <v>20930</v>
       </c>
-      <c r="D4" s="5" t="n">
-        <v>6794</v>
+      <c r="D4" s="17" t="n">
+        <v>0.2119423884776955</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>127665</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>8.67385849915679</v>
-      </c>
-      <c r="G4" s="7" t="n">
+        <v>4436</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>227479</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>10.09103267615629</v>
+      </c>
+      <c r="H4" s="7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2394,22 +2732,25 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>② 신청만 ×1.8 (연말 유입 증가)</t>
+          <t>② 신청만 ×1.8 (유입 증가)</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
         <v>37675</v>
       </c>
-      <c r="D5" s="5" t="n">
-        <v>12230</v>
+      <c r="D5" s="17" t="n">
+        <v>0.2119423884776955</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>127665</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>15.61294529848222</v>
-      </c>
-      <c r="G5" s="7" t="n">
+        <v>7985</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>227479</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>18.16385881708132</v>
+      </c>
+      <c r="H5" s="7" t="n">
         <v>1.8</v>
       </c>
     </row>
@@ -2421,23 +2762,26 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>③ 믹스만 +150% (대량입금 유입)</t>
+          <t>③ 믹스만 θ=+1.5 (대량입금 유입)</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
         <v>20930</v>
       </c>
-      <c r="D6" s="5" t="n">
-        <v>6794</v>
+      <c r="D6" s="17" t="n">
+        <v>0.3813403588857868</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>214977</v>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>14.60604761606191</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>1.683915827942294</v>
+        <v>7982</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>248434</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>19.82898611350473</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>1.965010594045332</v>
       </c>
     </row>
     <row r="7">
@@ -2448,23 +2792,26 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>④ worst — ×1.8 + 150% 동시</t>
-        </is>
-      </c>
-      <c r="C7" s="19" t="n">
+          <t>④ worst — ×1.8 + θ=+1.5 동시</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="n">
         <v>37675</v>
       </c>
       <c r="D7" s="19" t="n">
-        <v>12230</v>
-      </c>
-      <c r="E7" s="19" t="n">
-        <v>214977</v>
-      </c>
-      <c r="F7" s="18" t="n">
-        <v>26.29088570891144</v>
-      </c>
-      <c r="G7" s="20" t="n">
-        <v>3.031048490296129</v>
+        <v>0.3813403588857868</v>
+      </c>
+      <c r="E7" s="20" t="n">
+        <v>14367</v>
+      </c>
+      <c r="F7" s="20" t="n">
+        <v>248434</v>
+      </c>
+      <c r="G7" s="25" t="n">
+        <v>35.69217500430851</v>
+      </c>
+      <c r="H7" s="21" t="n">
+        <v>3.537019069281599</v>
       </c>
     </row>
     <row r="9">
@@ -2475,22 +2822,25 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>① 기준 (신청 유지 · 믹스 현행유지)</t>
+          <t>① 기준 (신청 유지 · 믹스 = 실측 10회차 평균)</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
         <v>26132</v>
       </c>
-      <c r="D9" s="5" t="n">
-        <v>8483</v>
+      <c r="D9" s="17" t="n">
+        <v>0.2119423884776955</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>127665</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>10.82950180767931</v>
-      </c>
-      <c r="G9" s="7" t="n">
+        <v>5538</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>227479</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>12.59887472436967</v>
+      </c>
+      <c r="H9" s="7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2502,22 +2852,25 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>② 신청만 ×1.8 (연말 유입 증가)</t>
+          <t>② 신청만 ×1.8 (유입 증가)</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
         <v>47038</v>
       </c>
-      <c r="D10" s="5" t="n">
-        <v>15269</v>
+      <c r="D10" s="17" t="n">
+        <v>0.2119423884776955</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>127665</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>19.49310325382275</v>
-      </c>
-      <c r="G10" s="7" t="n">
+        <v>9969</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>227479</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>22.67797450386539</v>
+      </c>
+      <c r="H10" s="7" t="n">
         <v>1.8</v>
       </c>
     </row>
@@ -2529,23 +2882,26 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>③ 믹스만 +150% (대량입금 유입)</t>
+          <t>③ 믹스만 θ=+1.5 (대량입금 유입)</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
         <v>26132</v>
       </c>
-      <c r="D11" s="5" t="n">
-        <v>8483</v>
+      <c r="D11" s="17" t="n">
+        <v>0.3813403588857868</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>214977</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>18.23596950268087</v>
-      </c>
-      <c r="G11" s="7" t="n">
-        <v>1.683915827942295</v>
+        <v>9965</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>248434</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>24.75692230643635</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>1.965010594045332</v>
       </c>
     </row>
     <row r="12">
@@ -2556,23 +2912,26 @@
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>④ worst — ×1.8 + 150% 동시</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="n">
+          <t>④ worst — ×1.8 + θ=+1.5 동시</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="n">
         <v>47038</v>
       </c>
       <c r="D12" s="19" t="n">
-        <v>15269</v>
-      </c>
-      <c r="E12" s="19" t="n">
-        <v>214977</v>
-      </c>
-      <c r="F12" s="18" t="n">
-        <v>32.82474510482557</v>
-      </c>
-      <c r="G12" s="20" t="n">
-        <v>3.03104849029613</v>
+        <v>0.3813403588857868</v>
+      </c>
+      <c r="E12" s="20" t="n">
+        <v>17937</v>
+      </c>
+      <c r="F12" s="20" t="n">
+        <v>248434</v>
+      </c>
+      <c r="G12" s="25" t="n">
+        <v>44.56246015158543</v>
+      </c>
+      <c r="H12" s="21" t="n">
+        <v>3.537019069281598</v>
       </c>
     </row>
     <row r="14">
@@ -2583,22 +2942,25 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>① 기준 (신청 유지 · 믹스 현행유지)</t>
+          <t>① 기준 (신청 유지 · 믹스 = 실측 10회차 평균)</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
         <v>26786</v>
       </c>
-      <c r="D14" s="5" t="n">
-        <v>8695</v>
+      <c r="D14" s="17" t="n">
+        <v>0.2119423884776955</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>127665</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>11.10063484000036</v>
-      </c>
-      <c r="G14" s="7" t="n">
+        <v>5677</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>227479</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>12.91430669608134</v>
+      </c>
+      <c r="H14" s="7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2610,22 +2972,25 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>② 신청만 ×1.8 (연말 유입 증가)</t>
+          <t>② 신청만 ×1.8 (유입 증가)</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
         <v>48215</v>
       </c>
-      <c r="D15" s="5" t="n">
-        <v>15651</v>
+      <c r="D15" s="17" t="n">
+        <v>0.2119423884776955</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>127665</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>19.98114271200065</v>
-      </c>
-      <c r="G15" s="7" t="n">
+        <v>10219</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>227479</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>23.24575205294641</v>
+      </c>
+      <c r="H15" s="7" t="n">
         <v>1.8</v>
       </c>
     </row>
@@ -2637,23 +3002,26 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>③ 믹스만 +150% (대량입금 유입)</t>
+          <t>③ 믹스만 θ=+1.5 (대량입금 유입)</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
         <v>26786</v>
       </c>
-      <c r="D16" s="5" t="n">
-        <v>8695</v>
+      <c r="D16" s="17" t="n">
+        <v>0.3813403588857868</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>214977</v>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>18.69253470728428</v>
-      </c>
-      <c r="G16" s="7" t="n">
-        <v>1.683915827942294</v>
+        <v>10215</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>248434</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>25.3767494725504</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>1.965010594045333</v>
       </c>
     </row>
     <row r="17">
@@ -2664,29 +3032,32 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>④ worst — ×1.8 + 150% 동시</t>
-        </is>
-      </c>
-      <c r="C17" s="19" t="n">
+          <t>④ worst — ×1.8 + θ=+1.5 동시</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="n">
         <v>48215</v>
       </c>
       <c r="D17" s="19" t="n">
-        <v>15651</v>
-      </c>
-      <c r="E17" s="19" t="n">
-        <v>214977</v>
-      </c>
-      <c r="F17" s="18" t="n">
-        <v>33.64656247311171</v>
-      </c>
-      <c r="G17" s="20" t="n">
-        <v>3.03104849029613</v>
+        <v>0.3813403588857868</v>
+      </c>
+      <c r="E17" s="20" t="n">
+        <v>18386</v>
+      </c>
+      <c r="F17" s="20" t="n">
+        <v>248434</v>
+      </c>
+      <c r="G17" s="25" t="n">
+        <v>45.67814905059073</v>
+      </c>
+      <c r="H17" s="21" t="n">
+        <v>3.537019069281599</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>※ 두 축은 곱으로 작용한다. 신청 배수는 총예산에 정비례하고, 믹스 상향은 평균 단가를 통해 곱해진다 → worst 배율 ≈ 신청배수 × 단가배율.</t>
+          <t>※ 두 축은 곱으로 작용한다. 신청 배수는 총예산에 정비례하고, 믹스 상향은 지급률과 평균 단가를 함께 올린다 → worst 배율 ≈ 신청배수 × 신청1인당 배율.</t>
         </is>
       </c>
     </row>

--- a/reports/리워드유지_신청자·이전금액구간_스트레스테스트.xlsx
+++ b/reports/리워드유지_신청자·이전금액구간_스트레스테스트.xlsx
@@ -563,16 +563,16 @@
         <v>20930</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>10.09103267615629</v>
+        <v>9.382297070953255</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>35.69217500430851</v>
+        <v>37.08678701548362</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>3.537019069281599</v>
+        <v>3.952847232934134</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>20.18347392915378</v>
+        <v>19.77094877432375</v>
       </c>
     </row>
     <row r="6">
@@ -585,16 +585,16 @@
         <v>26132</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>12.59887472436967</v>
+        <v>11.71400283967624</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>44.56246015158543</v>
+        <v>46.30366371139683</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>3.537019069281598</v>
+        <v>3.952847232934134</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>25.25812766587075</v>
+        <v>24.68323402377694</v>
       </c>
     </row>
     <row r="7">
@@ -607,16 +607,16 @@
         <v>26786</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>12.91430669608134</v>
+        <v>12.00728069926224</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>45.67814905059073</v>
+        <v>47.46294628714218</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>3.537019069281599</v>
+        <v>3.952847232934135</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>25.96028242180204</v>
+        <v>25.41374660059781</v>
       </c>
     </row>
     <row r="8">
@@ -627,16 +627,16 @@
       </c>
       <c r="B8" s="8" t="inlineStr"/>
       <c r="C8" s="9" t="n">
-        <v>35.60421409660729</v>
+        <v>33.10358060989174</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>125.9327842064847</v>
+        <v>130.8533970140226</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>3.537019069281599</v>
+        <v>3.952847232934134</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>61.26466555480935</v>
+        <v>59.78251129462576</v>
       </c>
     </row>
     <row r="10">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>35.60421409660729</v>
+        <v>33.10358060989174</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>45.82356405048272</v>
+        <v>44.12829326827499</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>61.26466555480935</v>
+        <v>59.78251129462576</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>71.40188401682657</v>
+        <v>69.86792939869851</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>125.9327842064847</v>
+        <v>130.8533970140226</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>핵심: 리워드를 현재안대로 유지해도 신청자 1.8배 + 대량입금 믹스 상향이 겹치면 예산은 기준 대비 약 3.5배로 늘어난다. 편성 권고는 3회차 합 61.3~71.4억원(P90 범위).</t>
+          <t>핵심: 리워드를 현재안대로 유지해도 신청자 1.8배 + 대량입금 믹스 상향이 겹치면 예산은 기준 대비 약 4.0배로 늘어난다. 편성 권고는 3회차 합 59.8~69.9억원(P90 범위).</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -821,7 +821,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>21.19% — 실측 금액 분포에서 유도(수관 5백만원 이상 비중)</t>
+          <t>19.91% — 실측 금액 분포에서 유도(수관 5백만원 이상 비중)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>기울기 θ = -1.0, +0.0, +0.5, +1.0, +1.5. θ=0 실측 10회차 평균, θ=+1 관측 최고(1470), θ=-1 관측 최저(1536), |θ|&gt;1 은 관측 범위 외삽</t>
+          <t>기울기 θ = -1.0, +0.0, +0.5, +1.0, +1.5. θ=0 실측 10회차 가중, θ=+1 관측 최고(1470), θ=-1 관측 최저(1536), |θ|&gt;1 은 관측 범위 외삽</t>
         </is>
       </c>
     </row>
@@ -871,82 +871,86 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>data/transfer_amount_distribution.csv — 이벤트 회차별 타사수관금액 구간 분포</t>
+          <t>data/transfer_amount_distribution.csv — 이벤트 회차별 타사수관금액 구간별 고객 수(실측)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>사용 회차</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>성숙 10회차 단순평균 (회차별 고객 수가 없어 가중평균 불가). 진행 초기라 수관 실적이 안 잡힌 1647 제외</t>
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>교차 검증</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>회차별 총 고객 수가 reference_deposit_events.csv 의 신청자수와 10건 중 9건 정확히 일치(1607 은 진행 경과로 16,356 → 17,399). 분포의 모집단이 '신청 고객'임이 확인된다</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>구간 내부 보간</t>
+          <t>사용 회차</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>로그축 균등. 1.5배 인정 때문에 리워드 구간 경계가 실측 구간 안쪽(예: 실제 2,000만원)에 떨어져 쪼개 적분해야 한다. 구간 경계에서는 실측치를 정확히 재현</t>
+          <t>10회차, 고객 수 가중 통합 (총 신청 100,058명, 리워드 대상 19,920명). 회차 규모가 4,063~19,831명으로 5배 차이나 가중이 맞다</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
+          <t>구간 내부 보간</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>로그축 균등. 1.5배 인정 때문에 리워드 구간 경계가 실측 구간 안쪽(예: 실제 2,000만원)에 떨어져 쪼개 적분해야 한다. 구간 경계에서는 실측치를 정확히 재현</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
           <t>대상자 평균 수관금액</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>5,493만원</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>5,476만원</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>치환 효과</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>이전(로그정규 가정) 지급률 32.5%×단가 12.8만원 = 41,442원/신청 → 실측 21.19%×22.7만원 = 48,213원/신청 (+16.3%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>이전(로그정규 가정) 지급률 32.5%×단가 12.8만원 = 41,442원/신청 → 실측 19.91%×22.5만원 = 44,826원/신청 (+8.2%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>해석</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>분해는 크게 달라졌지만(대상자 적고 단가 높음) 곱인 신청 1인당 예산은 수렴한다 — 두 방식이 같은 총예산을 다르게 쪼개고 있었다는 뜻</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>[ 한계 ]</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr"/>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>지급률은 신청자 수와 독립이라고 가정. 유입 급증 시 질이 희석돼 지급률이 낮아질 수 있어 이 가정은 예산을 보수적(과대)으로 만든다.</t>
         </is>
       </c>
     </row>
@@ -954,7 +958,7 @@
       <c r="A23" s="4" t="inlineStr"/>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>2026_04는 시즌4 take-rate에 연말효과가 이미 일부 반영돼 있다. 배수 1.8은 모델 기준선 대비 '추가' 변동으로 해석해야 하며 연말효과를 이중 계상하지 않도록 주의.</t>
+          <t>지급률은 신청자 수와 독립이라고 가정. 유입 급증 시 질이 희석돼 지급률이 낮아질 수 있어 이 가정은 예산을 보수적(과대)으로 만든다.</t>
         </is>
       </c>
     </row>
@@ -962,7 +966,7 @@
       <c r="A24" s="4" t="inlineStr"/>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>믹스 시프트는 분포 전체의 중앙값 상향으로 모델링. 대량입금 고객 신규 유입 시 조건충족률도 함께 오를 수 있으나 지급률은 고정했다.</t>
+          <t>2026_04는 시즌4 take-rate에 연말효과가 이미 일부 반영돼 있다. 배수 1.8은 모델 기준선 대비 '추가' 변동으로 해석해야 하며 연말효과를 이중 계상하지 않도록 주의.</t>
         </is>
       </c>
     </row>
@@ -970,7 +974,7 @@
       <c r="A25" s="4" t="inlineStr"/>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>몬테카를로 P50이 기준셀보다 높은 것은 정상이다. 두 축 모두 최빈값에서 위쪽으로 더 멀리 뻗은 삼각분포라 중앙값이 최빈값 위에 형성된다(상방 비대칭 설정의 귀결).</t>
+          <t>믹스 시프트는 분포 전체의 중앙값 상향으로 모델링. 대량입금 고객 신규 유입 시 조건충족률도 함께 오를 수 있으나 지급률은 고정했다.</t>
         </is>
       </c>
     </row>
@@ -978,13 +982,21 @@
       <c r="A26" s="4" t="inlineStr"/>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>연말효과 가정은 실측과 어긋난다. 유일한 12월 단독 회차 1536(202512)이 10회차 중 최저이고 최고는 9월 회차 1470(202509)이다. 축2 상향은 계절 효과가 아니라 일반적인 상방 리스크로 읽어야 한다.</t>
+          <t>몬테카를로 P50이 기준셀보다 높은 것은 정상이다. 두 축 모두 최빈값에서 위쪽으로 더 멀리 뻗은 삼각분포라 중앙값이 최빈값 위에 형성된다(상방 비대칭 설정의 귀결).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr"/>
       <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>연말효과 가정은 실측과 어긋난다. 유일한 12월 단독 회차 1536(202512)이 10회차 중 최저이고 최고는 9월 회차 1470(202509)이다. 축2 상향은 계절 효과가 아니라 일반적인 상방 리스크로 읽어야 한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr"/>
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>최저 구간 [0, 5백만)의 하한은 10만원으로 가정했다(로그축 보간용). 대상자 평균 수관금액 계산에만 영향을 준다.</t>
         </is>
@@ -1070,7 +1082,7 @@
         <v>10000000</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>0.05615856536101956</v>
+        <v>0.05732931726907646</v>
       </c>
     </row>
     <row r="5">
@@ -1092,7 +1104,7 @@
         <v>20000000</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.1473856668324076</v>
+        <v>0.1546601398940474</v>
       </c>
     </row>
     <row r="6">
@@ -1114,7 +1126,7 @@
         <v>33333333.33333333</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.1346885012625715</v>
+        <v>0.1393317766062913</v>
       </c>
     </row>
     <row r="7">
@@ -1136,7 +1148,7 @@
         <v>66666666.66666666</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.3463687764125888</v>
+        <v>0.3417167478912654</v>
       </c>
     </row>
     <row r="8">
@@ -1158,7 +1170,7 @@
         <v>133333333.3333333</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.2614966200826097</v>
+        <v>0.2522496268366135</v>
       </c>
     </row>
     <row r="9">
@@ -1180,7 +1192,7 @@
         <v>200000000</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.05107034574488645</v>
+        <v>0.05024452001676229</v>
       </c>
     </row>
     <row r="10">
@@ -1204,7 +1216,7 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.002831524303917367</v>
+        <v>0.004467871485943538</v>
       </c>
     </row>
     <row r="11">
@@ -1214,10 +1226,10 @@
         </is>
       </c>
       <c r="B11" s="14" t="n">
-        <v>178978</v>
+        <v>177240</v>
       </c>
       <c r="C11" s="14" t="n">
-        <v>227479</v>
+        <v>225162</v>
       </c>
       <c r="D11" s="8" t="inlineStr"/>
       <c r="E11" s="8" t="inlineStr"/>
@@ -1358,40 +1370,40 @@
         </is>
       </c>
       <c r="C4" s="17" t="n">
-        <v>0.1370000017260002</v>
+        <v>0.1368266904367758</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>0.06569342969790574</v>
+        <v>0.06375058166589097</v>
       </c>
       <c r="E4" s="13" t="n">
-        <v>0.1796077374457759</v>
+        <v>0.1802656438775591</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>0.1547457351213028</v>
+        <v>0.1544930725897581</v>
       </c>
       <c r="G4" s="13" t="n">
-        <v>0.3305496196739464</v>
+        <v>0.3287602165141449</v>
       </c>
       <c r="H4" s="13" t="n">
-        <v>0.2267054713324864</v>
+        <v>0.2282474699429746</v>
       </c>
       <c r="I4" s="13" t="n">
-        <v>0.04269799213004082</v>
+        <v>0.04355234998389259</v>
       </c>
       <c r="J4" s="13" t="n">
-        <v>1.459853954919018e-08</v>
+        <v>0.0009306654257797381</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>204008</v>
+        <v>206075</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>27949</v>
+        <v>28197</v>
       </c>
       <c r="M4" s="7" t="n">
-        <v>0.5797062855471036</v>
+        <v>0.6290185983462363</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>4984</v>
+        <v>5043</v>
       </c>
     </row>
     <row r="5">
@@ -1404,40 +1416,40 @@
         </is>
       </c>
       <c r="C5" s="17" t="n">
-        <v>0.2119423884776955</v>
+        <v>0.1990845309720363</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>0.05615856536101956</v>
+        <v>0.05732931726907646</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>0.1473856668324076</v>
+        <v>0.1546601398940474</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.1346885012625715</v>
+        <v>0.1393317766062913</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>0.3463687764125888</v>
+        <v>0.3417167478912654</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>0.2614966200826097</v>
+        <v>0.2522496268366135</v>
       </c>
       <c r="I5" s="13" t="n">
-        <v>0.05107034574488645</v>
+        <v>0.05024452001676229</v>
       </c>
       <c r="J5" s="13" t="n">
-        <v>0.002831524303917367</v>
+        <v>0.004467871485943538</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>227479</v>
+        <v>225162</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>48213</v>
+        <v>44826</v>
       </c>
       <c r="M5" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>5493</v>
+        <v>5476</v>
       </c>
     </row>
     <row r="6">
@@ -1450,40 +1462,40 @@
         </is>
       </c>
       <c r="C6" s="17" t="n">
-        <v>0.2601515201290148</v>
+        <v>0.2524409835612083</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>0.0567388134088113</v>
+        <v>0.05663054654495708</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>0.1276249157796092</v>
+        <v>0.1312086067491923</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.1231965151047397</v>
+        <v>0.1255900811338893</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>0.3593908980344281</v>
+        <v>0.3574761232262085</v>
       </c>
       <c r="H6" s="13" t="n">
-        <v>0.2805187531508026</v>
+        <v>0.2759985890264432</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>0.05252709770877667</v>
+        <v>0.05223222298941542</v>
       </c>
       <c r="J6" s="13" t="n">
-        <v>3.006812833356627e-06</v>
+        <v>0.0008638303298941775</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>233131</v>
+        <v>232227</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>60649</v>
+        <v>58623</v>
       </c>
       <c r="M6" s="7" t="n">
-        <v>1.257960709514796</v>
+        <v>1.307791371269716</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>5626</v>
+        <v>5631</v>
       </c>
     </row>
     <row r="7">
@@ -1496,40 +1508,40 @@
         </is>
       </c>
       <c r="C7" s="17" t="n">
-        <v>0.3170000013660002</v>
+        <v>0.3172891805055834</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>0.05678233402660996</v>
+        <v>0.05521844642790993</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>0.1094673067113423</v>
+        <v>0.1098767225147503</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.1121822047828263</v>
+        <v>0.1124584152076327</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>0.3698971327178932</v>
+        <v>0.3700328743496028</v>
       </c>
       <c r="H7" s="13" t="n">
-        <v>0.2981570961654739</v>
+        <v>0.2982088433682136</v>
       </c>
       <c r="I7" s="13" t="n">
-        <v>0.05351391928670561</v>
+        <v>0.05359789886559914</v>
       </c>
       <c r="J7" s="13" t="n">
-        <v>6.309148059362271e-09</v>
+        <v>0.0006067992662912385</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>241118</v>
+        <v>242013</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>76434</v>
+        <v>76788</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>1.585365872494873</v>
+        <v>1.713013574526431</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>5799</v>
+        <v>5837</v>
       </c>
     </row>
     <row r="8">
@@ -1542,53 +1554,53 @@
         </is>
       </c>
       <c r="C8" s="17" t="n">
-        <v>0.3813403588857868</v>
+        <v>0.392222908756043</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>0.05647793198057001</v>
+        <v>0.0533643912501412</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>0.09331811386919239</v>
+        <v>0.09119751708431822</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.1020534875082248</v>
+        <v>0.1004658864981978</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>0.3789179506227197</v>
+        <v>0.3805601990791849</v>
       </c>
       <c r="H8" s="13" t="n">
-        <v>0.3150470655109336</v>
+        <v>0.3194761006721556</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>0.0541854479536162</v>
+        <v>0.05451185557436795</v>
       </c>
       <c r="J8" s="13" t="n">
-        <v>2.554742936564946e-09</v>
+        <v>0.0004240498416343119</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>248434</v>
+        <v>250979</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>94738</v>
+        <v>98440</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>1.965010594045332</v>
+        <v>2.196026240518964</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>5958</v>
+        <v>6028</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>※ θ=0 은 실측 10회차 평균, θ=+1 은 관측 최고 회차(1470), θ=-1 은 관측 최저 회차(1536). |θ|&gt;1 은 관측 범위를 벗어난 외삽 구간이다.</t>
+          <t>※ θ=0 은 실측 10회차 가중 통합, θ=+1 은 관측 최고 회차(1470), θ=-1 은 관측 최저 회차(1536). |θ|&gt;1 은 관측 범위를 벗어난 외삽 구간이다.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>※ 회차 간 변동은 대상자 내부 믹스가 아니라 '지급률'에 거의 전부 몰려 있다(단가 20.4~24.1만원 ±9% vs 지급률 13.7~31.7% ±40%). 그래서 축2는 금액축을 미는 대신 관측된 변동 방향을 그대로 기울기로 쓴다.</t>
+          <t>※ 회차 간 변동은 대상자 내부 믹스가 아니라 '지급률'에 거의 전부 몰려 있다(단가 ±9% vs 지급률 13.7~31.7% ±40%). 그래서 축2는 금액축을 미는 대신 관측된 변동 방향을 그대로 기울기로 쓴다.</t>
         </is>
       </c>
     </row>
@@ -1638,19 +1650,19 @@
         </is>
       </c>
       <c r="B16" s="19" t="n">
-        <v>0.137</v>
+        <v>0.1368266904367758</v>
       </c>
       <c r="C16" s="20" t="n">
-        <v>204008</v>
+        <v>206075</v>
       </c>
       <c r="D16" s="20" t="n">
-        <v>27949</v>
+        <v>28197</v>
       </c>
       <c r="E16" s="21" t="n">
-        <v>0.5797062335231654</v>
+        <v>0.6290185983462363</v>
       </c>
       <c r="F16" s="22" t="n">
-        <v>-1.000000164998106</v>
+        <v>-0.9999999999999958</v>
       </c>
     </row>
     <row r="17">
@@ -1660,19 +1672,19 @@
         </is>
       </c>
       <c r="B17" s="17" t="n">
-        <v>0.1679999999999999</v>
+        <v>0.1682881391016353</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>217312</v>
+        <v>221951</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>36508</v>
+        <v>37352</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>0.7572403530657924</v>
+        <v>0.8332551540407503</v>
       </c>
       <c r="F17" s="23" t="n">
-        <v>-0.5031608307252122</v>
+        <v>-0.3915260934049876</v>
       </c>
     </row>
     <row r="18">
@@ -1682,19 +1694,19 @@
         </is>
       </c>
       <c r="B18" s="17" t="n">
-        <v>0.1779999999999999</v>
+        <v>0.178004134940245</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>222907</v>
+        <v>224292</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>39678</v>
+        <v>39925</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>0.8229716711714284</v>
+        <v>0.8906574325285089</v>
       </c>
       <c r="F18" s="23" t="n">
-        <v>-0.3458549672009231</v>
+        <v>-0.2478045844035355</v>
       </c>
     </row>
     <row r="19">
@@ -1704,19 +1716,19 @@
         </is>
       </c>
       <c r="B19" s="17" t="n">
-        <v>0.2070000000000001</v>
+        <v>0.2068252326783868</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>203971</v>
+        <v>207150</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>42222</v>
+        <v>42844</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>0.8757498407450347</v>
+        <v>0.9557748917505314</v>
       </c>
       <c r="F19" s="23" t="n">
-        <v>-0.2283583257726709</v>
+        <v>-0.09639285228442809</v>
       </c>
     </row>
     <row r="20">
@@ -1726,19 +1738,19 @@
         </is>
       </c>
       <c r="B20" s="17" t="n">
-        <v>0.195</v>
+        <v>0.1953673373888629</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>232954</v>
+        <v>234415</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>45426</v>
+        <v>45797</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>0.9422051528176612</v>
+        <v>1.021655803317958</v>
       </c>
       <c r="F20" s="23" t="n">
-        <v>-0.09470431495302611</v>
+        <v>0.05268488991931031</v>
       </c>
     </row>
     <row r="21">
@@ -1748,19 +1760,19 @@
         </is>
       </c>
       <c r="B21" s="17" t="n">
-        <v>0.222</v>
+        <v>0.2224956928378046</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>229158</v>
+        <v>231522</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>50873</v>
+        <v>51513</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>1.055181958945496</v>
+        <v>1.14915902835833</v>
       </c>
       <c r="F21" s="23" t="n">
-        <v>0.1338564785626885</v>
+        <v>0.2705384710793792</v>
       </c>
     </row>
     <row r="22">
@@ -1770,19 +1782,19 @@
         </is>
       </c>
       <c r="B22" s="17" t="n">
-        <v>0.227</v>
+        <v>0.2271969653428358</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>232586</v>
+        <v>234141</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>52797</v>
+        <v>53196</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>1.095089508805191</v>
+        <v>1.186716842087458</v>
       </c>
       <c r="F22" s="23" t="n">
-        <v>0.2123249580211938</v>
+        <v>0.3273117970223082</v>
       </c>
     </row>
     <row r="23">
@@ -1792,19 +1804,19 @@
         </is>
       </c>
       <c r="B23" s="17" t="n">
-        <v>0.233</v>
+        <v>0.2327252625760089</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>235344</v>
+        <v>233905</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>54835</v>
+        <v>54436</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>1.137365392513166</v>
+        <v>1.214369057763247</v>
       </c>
       <c r="F23" s="23" t="n">
-        <v>0.2907362583363667</v>
+        <v>0.3680349575260157</v>
       </c>
     </row>
     <row r="24">
@@ -1814,19 +1826,19 @@
         </is>
       </c>
       <c r="B24" s="17" t="n">
-        <v>0.237</v>
+        <v>0.2368217054263566</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>233357</v>
+        <v>231732</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>55306</v>
+        <v>54879</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>1.147124065930766</v>
+        <v>1.224262648431317</v>
       </c>
       <c r="F24" s="23" t="n">
-        <v>0.3083772101386267</v>
+        <v>0.3824055918979506</v>
       </c>
     </row>
     <row r="25">
@@ -1836,19 +1848,19 @@
         </is>
       </c>
       <c r="B25" s="19" t="n">
-        <v>0.3170000000000001</v>
+        <v>0.3172891798228725</v>
       </c>
       <c r="C25" s="20" t="n">
-        <v>241118</v>
+        <v>242013</v>
       </c>
       <c r="D25" s="20" t="n">
-        <v>76434</v>
+        <v>76788</v>
       </c>
       <c r="E25" s="21" t="n">
-        <v>1.585365822482256</v>
+        <v>1.713013547639043</v>
       </c>
       <c r="F25" s="22" t="n">
-        <v>0.9999999294263109</v>
+        <v>0.999999969812464</v>
       </c>
     </row>
     <row r="27">
@@ -1933,19 +1945,19 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>4.679868056023208</v>
+        <v>4.721311482271211</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>8.072826140925031</v>
+        <v>7.505837656762606</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>10.15529810002764</v>
+        <v>9.816069721665436</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>12.79838305840703</v>
+        <v>12.857601794226</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>15.86318889080378</v>
+        <v>16.48301645132605</v>
       </c>
     </row>
     <row r="6">
@@ -1955,19 +1967,19 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>5.26485156302611</v>
+        <v>5.311475417555115</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>9.08192940854066</v>
+        <v>8.444067363857931</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>11.4247103625311</v>
+        <v>11.04307843687361</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>14.39818094070791</v>
+        <v>14.46480201850425</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>17.84608750215425</v>
+        <v>18.54339350774181</v>
       </c>
     </row>
     <row r="7">
@@ -1977,19 +1989,19 @@
         </is>
       </c>
       <c r="B7" s="24" t="n">
-        <v>5.849835070029011</v>
+        <v>5.901639352839013</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>10.09103267615629</v>
+        <v>9.382297070953255</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>12.69412262503456</v>
+        <v>12.27008715208179</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>15.99797882300879</v>
+        <v>16.0720022427825</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>19.82898611350473</v>
+        <v>20.60377056415756</v>
       </c>
     </row>
     <row r="8">
@@ -1999,19 +2011,19 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>7.019802084034811</v>
+        <v>7.081967223406816</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>12.10923921138754</v>
+        <v>11.25875648514391</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>15.23294715004147</v>
+        <v>14.72410458249815</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>19.19757458761055</v>
+        <v>19.286402691339</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>23.79478333620566</v>
+        <v>24.72452467698908</v>
       </c>
     </row>
     <row r="9">
@@ -2021,19 +2033,19 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>8.774752605043513</v>
+        <v>8.852459029258522</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>15.13654901423443</v>
+        <v>14.07344560642988</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>19.04118393755184</v>
+        <v>18.40513072812269</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>23.99696823451319</v>
+        <v>24.10800336417375</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>29.74347917025709</v>
+        <v>30.90565584623634</v>
       </c>
     </row>
     <row r="10">
@@ -2043,25 +2055,25 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>10.52970312605222</v>
+        <v>10.62295083511023</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>18.16385881708132</v>
+        <v>16.88813472771586</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>22.8494207250622</v>
+        <v>22.08615687374722</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>28.79636188141582</v>
+        <v>28.92960403700851</v>
       </c>
       <c r="F10" s="25" t="n">
-        <v>35.69217500430851</v>
+        <v>37.08678701548362</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>기준셀 10.09억 → worst 35.69억 (×3.54) · 기준 당첨 4,436명</t>
+          <t>기준셀 9.38억 → worst 37.09억 (×3.95) · 기준 당첨 4,167명</t>
         </is>
       </c>
     </row>
@@ -2111,19 +2123,19 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>5.842917494830102</v>
+        <v>5.894660517789585</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>10.07909977949573</v>
+        <v>9.371202271740996</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>12.67911150988488</v>
+        <v>12.25557746940603</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>15.97906081588313</v>
+        <v>16.05299670112526</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>19.80553784514908</v>
+        <v>20.57940609395414</v>
       </c>
     </row>
     <row r="17">
@@ -2133,19 +2145,19 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>6.573282181683864</v>
+        <v>6.631493082513283</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>11.3389872519327</v>
+        <v>10.54260255570862</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>14.26400044862049</v>
+        <v>13.78752465308178</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>17.97644341786853</v>
+        <v>18.05962128876591</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>22.28123007579272</v>
+        <v>23.15183185569841</v>
       </c>
     </row>
     <row r="18">
@@ -2155,19 +2167,19 @@
         </is>
       </c>
       <c r="B18" s="24" t="n">
-        <v>7.303646868537626</v>
+        <v>7.368325647236983</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>12.59887472436967</v>
+        <v>11.71400283967624</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>15.84888938735609</v>
+        <v>15.31947183675753</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>19.97382601985392</v>
+        <v>20.06624587640656</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>24.75692230643635</v>
+        <v>25.72425761744269</v>
       </c>
     </row>
     <row r="19">
@@ -2177,19 +2189,19 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>8.764376242245152</v>
+        <v>8.841990776684378</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>15.1186496692436</v>
+        <v>14.05680340761149</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>19.01866726482731</v>
+        <v>18.38336620410904</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>23.96859122382471</v>
+        <v>24.07949505168788</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>29.70830676772363</v>
+        <v>30.86910914093122</v>
       </c>
     </row>
     <row r="20">
@@ -2199,19 +2211,19 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>10.95547030280644</v>
+        <v>11.05248847085547</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>18.8983120865545</v>
+        <v>17.57100425951436</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>23.77333408103414</v>
+        <v>22.9792077551363</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>29.96073902978088</v>
+        <v>30.09936881460985</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>37.13538345965453</v>
+        <v>38.58638642616402</v>
       </c>
     </row>
     <row r="21">
@@ -2221,25 +2233,25 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>13.14656436336773</v>
+        <v>13.26298616502657</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>22.67797450386539</v>
+        <v>21.08520511141724</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>28.52800089724098</v>
+        <v>27.57504930616356</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>35.95288683573705</v>
+        <v>36.11924257753182</v>
       </c>
       <c r="F21" s="25" t="n">
-        <v>44.56246015158543</v>
+        <v>46.30366371139683</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>기준셀 12.60억 → worst 44.56억 (×3.54) · 기준 당첨 5,538명</t>
+          <t>기준셀 11.71억 → worst 46.30억 (×3.95) · 기준 당첨 5,202명</t>
         </is>
       </c>
     </row>
@@ -2289,19 +2301,19 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>5.98920381216112</v>
+        <v>6.0422423003198</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>10.33144535686507</v>
+        <v>9.605824559409793</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>12.99655233143533</v>
+        <v>12.56241447272684</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>16.3791208823195</v>
+        <v>16.45490786478835</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>20.30139957804032</v>
+        <v>21.09464279428541</v>
       </c>
     </row>
     <row r="28">
@@ -2311,19 +2323,19 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>6.737854288681261</v>
+        <v>6.797522587859775</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>11.62287602647321</v>
+        <v>10.80655262933601</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>14.62112137286475</v>
+        <v>14.1327162818177</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>18.42651099260944</v>
+        <v>18.51177134788689</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>22.83907452529536</v>
+        <v>23.73147314357109</v>
       </c>
     </row>
     <row r="29">
@@ -2333,19 +2345,19 @@
         </is>
       </c>
       <c r="B29" s="24" t="n">
-        <v>7.486504765201401</v>
+        <v>7.552802875399747</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>12.91430669608134</v>
+        <v>12.00728069926224</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>16.24569041429416</v>
+        <v>15.70301809090855</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>20.47390110289938</v>
+        <v>20.56863483098543</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>25.3767494725504</v>
+        <v>26.36830349285676</v>
       </c>
     </row>
     <row r="30">
@@ -2355,19 +2367,19 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>8.98380571824168</v>
+        <v>9.063363450479697</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>15.49716803529761</v>
+        <v>14.40873683911468</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>19.49482849715299</v>
+        <v>18.84362170909026</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>24.56868132347925</v>
+        <v>24.68236179718252</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>30.45209936706048</v>
+        <v>31.64196419142811</v>
       </c>
     </row>
     <row r="31">
@@ -2377,19 +2389,19 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>11.2297571478021</v>
+        <v>11.32920431309962</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>19.37146004412201</v>
+        <v>18.01092104889336</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>24.36853562144125</v>
+        <v>23.55452713636283</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>30.71085165434907</v>
+        <v>30.85295224647814</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>38.06512420882561</v>
+        <v>39.55245523928514</v>
       </c>
     </row>
     <row r="32">
@@ -2399,32 +2411,32 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>13.47570857736252</v>
+        <v>13.59504517571955</v>
       </c>
       <c r="C32" s="6" t="n">
-        <v>23.24575205294641</v>
+        <v>21.61310525867203</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>29.2422427457295</v>
+        <v>28.2654325636354</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>36.85302198521888</v>
+        <v>37.02354269577378</v>
       </c>
       <c r="F32" s="25" t="n">
-        <v>45.67814905059073</v>
+        <v>47.46294628714218</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>기준셀 12.91억 → worst 45.68억 (×3.54) · 기준 당첨 5,677명</t>
+          <t>기준셀 12.01억 → worst 47.46억 (×3.95) · 기준 당첨 5,333명</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>※ 연두색=기준셀(신청 유지 · 믹스 = 실측 10회차 평균), 주황색=worst case.</t>
+          <t>※ 연두색=기준셀(신청 유지 · 믹스 = 실측 10회차 가중 통합), 주황색=worst case.</t>
         </is>
       </c>
     </row>
@@ -2510,19 +2522,19 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>13.29292930093409</v>
+        <v>12.85430667323347</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>12.34570939074941</v>
+        <v>11.8068144911166</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>20.18347392915378</v>
+        <v>19.77094877432375</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>23.20413553632055</v>
+        <v>22.93156357140861</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>29.52343428917947</v>
+        <v>29.53406289927499</v>
       </c>
     </row>
     <row r="8">
@@ -2532,19 +2544,19 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>16.61576465122281</v>
+        <v>16.06989554120808</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>15.49487155787047</v>
+        <v>14.80350877139816</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>25.25812766587075</v>
+        <v>24.68323402377694</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>28.92249157834407</v>
+        <v>28.56131931272352</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>36.75031915341793</v>
+        <v>36.82264041208674</v>
       </c>
     </row>
     <row r="9">
@@ -2554,19 +2566,19 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>17.058942493138</v>
+        <v>16.50092218925636</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>15.84496873698965</v>
+        <v>15.13499148958778</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>25.96028242180204</v>
+        <v>25.41374660059781</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>29.86600331114009</v>
+        <v>29.54346911951383</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>38.34256687908064</v>
+        <v>38.34867936181288</v>
       </c>
     </row>
     <row r="10">
@@ -2576,19 +2588,19 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>46.96763644529489</v>
+        <v>45.42512440369791</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>45.82356405048272</v>
+        <v>44.12829326827499</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>61.26466555480935</v>
+        <v>59.78251129462576</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>66.432120045487</v>
+        <v>65.13294714622531</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>76.78500243787725</v>
+        <v>75.98553334878349</v>
       </c>
     </row>
     <row r="11">
@@ -2600,17 +2612,17 @@
       <c r="B11" s="12" t="inlineStr"/>
       <c r="C11" s="12" t="inlineStr"/>
       <c r="D11" s="25" t="n">
-        <v>71.40188401682657</v>
+        <v>69.86792939869851</v>
       </c>
       <c r="E11" s="25" t="n">
-        <v>81.99263042580471</v>
+        <v>81.03635200364594</v>
       </c>
       <c r="F11" s="12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>※ 합산 P90은 회차별 충격이 독립이면 61.3억(분산효과 최대), 모든 회차가 함께 움직이면 71.4억이다. 실제 편성치는 그 사이이며, 연말 대량입금처럼 회차를 가로지르는 충격을 크게 볼수록 상단에 가깝다.</t>
+          <t>※ 합산 P90은 회차별 충격이 독립이면 59.8억(분산효과 최대), 모든 회차가 함께 움직이면 69.9억이다. 실제 편성치는 그 사이이며, 연말 대량입금처럼 회차를 가로지르는 충격을 크게 볼수록 상단에 가깝다.</t>
         </is>
       </c>
     </row>
@@ -2702,23 +2714,23 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>① 기준 (신청 유지 · 믹스 = 실측 10회차 평균)</t>
+          <t>① 기준 (신청 유지 · 믹스 = 실측 10회차 가중)</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
         <v>20930</v>
       </c>
       <c r="D4" s="17" t="n">
-        <v>0.2119423884776955</v>
+        <v>0.1990845309720363</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>4436</v>
+        <v>4167</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>227479</v>
+        <v>225162</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>10.09103267615629</v>
+        <v>9.382297070953255</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>1</v>
@@ -2739,16 +2751,16 @@
         <v>37675</v>
       </c>
       <c r="D5" s="17" t="n">
-        <v>0.2119423884776955</v>
+        <v>0.1990845309720363</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>7985</v>
+        <v>7500</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>227479</v>
+        <v>225162</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>18.16385881708132</v>
+        <v>16.88813472771586</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>1.8</v>
@@ -2769,19 +2781,19 @@
         <v>20930</v>
       </c>
       <c r="D6" s="17" t="n">
-        <v>0.3813403588857868</v>
+        <v>0.392222908756043</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>7982</v>
+        <v>8209</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>248434</v>
+        <v>250979</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>19.82898611350473</v>
+        <v>20.60377056415756</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>1.965010594045332</v>
+        <v>2.196026240518963</v>
       </c>
     </row>
     <row r="7">
@@ -2799,19 +2811,19 @@
         <v>37675</v>
       </c>
       <c r="D7" s="19" t="n">
-        <v>0.3813403588857868</v>
+        <v>0.392222908756043</v>
       </c>
       <c r="E7" s="20" t="n">
-        <v>14367</v>
+        <v>14777</v>
       </c>
       <c r="F7" s="20" t="n">
-        <v>248434</v>
+        <v>250979</v>
       </c>
       <c r="G7" s="25" t="n">
-        <v>35.69217500430851</v>
+        <v>37.08678701548362</v>
       </c>
       <c r="H7" s="21" t="n">
-        <v>3.537019069281599</v>
+        <v>3.952847232934134</v>
       </c>
     </row>
     <row r="9">
@@ -2822,23 +2834,23 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>① 기준 (신청 유지 · 믹스 = 실측 10회차 평균)</t>
+          <t>① 기준 (신청 유지 · 믹스 = 실측 10회차 가중)</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
         <v>26132</v>
       </c>
       <c r="D9" s="17" t="n">
-        <v>0.2119423884776955</v>
+        <v>0.1990845309720363</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>5538</v>
+        <v>5202</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>227479</v>
+        <v>225162</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>12.59887472436967</v>
+        <v>11.71400283967624</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>1</v>
@@ -2859,16 +2871,16 @@
         <v>47038</v>
       </c>
       <c r="D10" s="17" t="n">
-        <v>0.2119423884776955</v>
+        <v>0.1990845309720363</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>9969</v>
+        <v>9364</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>227479</v>
+        <v>225162</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>22.67797450386539</v>
+        <v>21.08520511141724</v>
       </c>
       <c r="H10" s="7" t="n">
         <v>1.8</v>
@@ -2889,19 +2901,19 @@
         <v>26132</v>
       </c>
       <c r="D11" s="17" t="n">
-        <v>0.3813403588857868</v>
+        <v>0.392222908756043</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>9965</v>
+        <v>10250</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>248434</v>
+        <v>250979</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>24.75692230643635</v>
+        <v>25.72425761744269</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>1.965010594045332</v>
+        <v>2.196026240518963</v>
       </c>
     </row>
     <row r="12">
@@ -2919,19 +2931,19 @@
         <v>47038</v>
       </c>
       <c r="D12" s="19" t="n">
-        <v>0.3813403588857868</v>
+        <v>0.392222908756043</v>
       </c>
       <c r="E12" s="20" t="n">
-        <v>17937</v>
+        <v>18449</v>
       </c>
       <c r="F12" s="20" t="n">
-        <v>248434</v>
+        <v>250979</v>
       </c>
       <c r="G12" s="25" t="n">
-        <v>44.56246015158543</v>
+        <v>46.30366371139683</v>
       </c>
       <c r="H12" s="21" t="n">
-        <v>3.537019069281598</v>
+        <v>3.952847232934134</v>
       </c>
     </row>
     <row r="14">
@@ -2942,23 +2954,23 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>① 기준 (신청 유지 · 믹스 = 실측 10회차 평균)</t>
+          <t>① 기준 (신청 유지 · 믹스 = 실측 10회차 가중)</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
         <v>26786</v>
       </c>
       <c r="D14" s="17" t="n">
-        <v>0.2119423884776955</v>
+        <v>0.1990845309720363</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>5677</v>
+        <v>5333</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>227479</v>
+        <v>225162</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>12.91430669608134</v>
+        <v>12.00728069926224</v>
       </c>
       <c r="H14" s="7" t="n">
         <v>1</v>
@@ -2979,16 +2991,16 @@
         <v>48215</v>
       </c>
       <c r="D15" s="17" t="n">
-        <v>0.2119423884776955</v>
+        <v>0.1990845309720363</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>10219</v>
+        <v>9599</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>227479</v>
+        <v>225162</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>23.24575205294641</v>
+        <v>21.61310525867203</v>
       </c>
       <c r="H15" s="7" t="n">
         <v>1.8</v>
@@ -3009,19 +3021,19 @@
         <v>26786</v>
       </c>
       <c r="D16" s="17" t="n">
-        <v>0.3813403588857868</v>
+        <v>0.392222908756043</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>10215</v>
+        <v>10506</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>248434</v>
+        <v>250979</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>25.3767494725504</v>
+        <v>26.36830349285676</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>1.965010594045333</v>
+        <v>2.196026240518963</v>
       </c>
     </row>
     <row r="17">
@@ -3039,19 +3051,19 @@
         <v>48215</v>
       </c>
       <c r="D17" s="19" t="n">
-        <v>0.3813403588857868</v>
+        <v>0.392222908756043</v>
       </c>
       <c r="E17" s="20" t="n">
-        <v>18386</v>
+        <v>18911</v>
       </c>
       <c r="F17" s="20" t="n">
-        <v>248434</v>
+        <v>250979</v>
       </c>
       <c r="G17" s="25" t="n">
-        <v>45.67814905059073</v>
+        <v>47.46294628714218</v>
       </c>
       <c r="H17" s="21" t="n">
-        <v>3.537019069281599</v>
+        <v>3.952847232934135</v>
       </c>
     </row>
     <row r="19">

--- a/reports/리워드유지_신청자·이전금액구간_스트레스테스트.xlsx
+++ b/reports/리워드유지_신청자·이전금액구간_스트레스테스트.xlsx
@@ -674,7 +674,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>신청 현 수준 유지 + 금액 구간 믹스 = 실측 10회차 평균</t>
+          <t>신청 현 수준 유지 + 금액 구간 믹스 = 실측 10회차 고객 수 가중</t>
         </is>
       </c>
     </row>

--- a/reports/리워드유지_신청자·이전금액구간_스트레스테스트.xlsx
+++ b/reports/리워드유지_신청자·이전금액구간_스트레스테스트.xlsx
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>실측평균</t>
+          <t>실측가중</t>
         </is>
       </c>
       <c r="C5" s="17" t="n">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>θ=+0.0 실측평균</t>
+          <t>θ=+0.0 실측가중</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>θ=+0.0 실측평균</t>
+          <t>θ=+0.0 실측가중</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>θ=+0.0 실측평균</t>
+          <t>θ=+0.0 실측가중</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -2479,7 +2479,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>기울기 밴드는 실측 관측 범위에서 왔고 최빈값은 10회차 평균(θ=0)이다 — 임의 가정이 아니라 데이터가 눈금이다.</t>
+          <t>기울기 밴드는 실측 관측 범위에서 왔고 최빈값은 10회차 고객 수 가중 통합(θ=0)이다 — 임의 가정이 아니라 데이터가 눈금이다.</t>
         </is>
       </c>
     </row>

--- a/reports/리워드유지_신청자·이전금액구간_스트레스테스트.xlsx
+++ b/reports/리워드유지_신청자·이전금액구간_스트레스테스트.xlsx
@@ -572,7 +572,7 @@
         <v>3.952847232934134</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>19.77094877432375</v>
+        <v>13.77885918429242</v>
       </c>
     </row>
     <row r="6">
@@ -594,7 +594,7 @@
         <v>3.952847232934134</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>24.68323402377694</v>
+        <v>17.23406105264504</v>
       </c>
     </row>
     <row r="7">
@@ -616,7 +616,7 @@
         <v>3.952847232934135</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>25.41374660059781</v>
+        <v>17.66825007169669</v>
       </c>
     </row>
     <row r="8">
@@ -636,7 +636,7 @@
         <v>3.952847232934134</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>59.78251129462576</v>
+        <v>42.66543663573103</v>
       </c>
     </row>
     <row r="10">
@@ -685,11 +685,11 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>44.12829326827499</v>
+        <v>33.59569072772373</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>배수·기울기 상방 비대칭이 반영된 중앙값</t>
+          <t>밴드가 관측 범위로 대칭에 가까워 기준셀 근처에 놓인다</t>
         </is>
       </c>
     </row>
@@ -700,11 +700,11 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>59.78251129462576</v>
+        <v>42.66543663573103</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>회차별 충격이 독립일 때 — 분산효과 최대, 하한</t>
+          <t>회차별 충격이 독립일 때 — 분산효과 최대, 하한. MC 밴드: 배수 0.8~1.2 · θ -1.0~+1.0</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>69.86792939869851</v>
+        <v>48.68117030863415</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>핵심: 리워드를 현재안대로 유지해도 신청자 1.8배 + 대량입금 믹스 상향이 겹치면 예산은 기준 대비 약 4.0배로 늘어난다. 편성 권고는 3회차 합 59.8~69.9억원(P90 범위).</t>
+          <t>핵심: 리워드를 현재안대로 유지해도 신청자 1.8배 + 대량입금 믹스 상향이 겹치면 예산은 기준 대비 약 4.0배로 늘어난다. 편성 권고는 3회차 합 42.7~48.7억원(P90 범위).</t>
         </is>
       </c>
     </row>
@@ -2472,14 +2472,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>방법: 40,000회 시뮬레이션. 신청배수 삼각(0.8/1.0/1.8), 믹스 기울기 삼각(θ=-1.0/0/+1.5), 지급률은 기울기에서 유도 후 잔여 잡음 CV 0.22.</t>
+          <t>방법: 40,000회 시뮬레이션. 신청배수 삼각(0.8/1.0/1.2), 믹스 기울기 삼각(θ=-1.0/+0.0/+1.0), 지급률은 기울기에서 유도 후 잔여 잡음 CV 0.22.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>기울기 밴드는 실측 관측 범위에서 왔고 최빈값은 10회차 고객 수 가중 통합(θ=0)이다 — 임의 가정이 아니라 데이터가 눈금이다.</t>
+          <t>밴드를 관측 범위로 제한했다 — 기울기 -1.0~+1.0 는 실측 회차 최저(1536)~최고(1470) 그 자체이고 신청 배수는 0.8~1.2다. 관측 범위를 넘는 극단(배수 1.8·θ=+1.5)은 결정론 매트릭스의 worst case 가 담당한다.</t>
         </is>
       </c>
     </row>
@@ -2522,19 +2522,19 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>12.85430667323347</v>
+        <v>9.671173972578575</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>11.8068144911166</v>
+        <v>9.198907181847725</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>19.77094877432375</v>
+        <v>13.77885918429242</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>22.93156357140861</v>
+        <v>15.46646483679792</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>29.53406289927499</v>
+        <v>19.06554148824232</v>
       </c>
     </row>
     <row r="8">
@@ -2544,19 +2544,19 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>16.06989554120808</v>
+        <v>12.09630222410399</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>14.80350877139816</v>
+        <v>11.52313235166203</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>24.68323402377694</v>
+        <v>17.23406105264504</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>28.56131931272352</v>
+        <v>19.30041578638071</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>36.82264041208674</v>
+        <v>23.6951316556239</v>
       </c>
     </row>
     <row r="9">
@@ -2566,19 +2566,19 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>16.50092218925636</v>
+        <v>12.41595426969426</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>15.13499148958778</v>
+        <v>11.78215123453676</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>25.41374660059781</v>
+        <v>17.66825007169669</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>29.54346911951383</v>
+        <v>19.86860949102268</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>38.34867936181288</v>
+        <v>24.76052284701722</v>
       </c>
     </row>
     <row r="10">
@@ -2588,19 +2588,19 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>45.42512440369791</v>
+        <v>34.18343046637683</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>44.12829326827499</v>
+        <v>33.59569072772373</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>59.78251129462576</v>
+        <v>42.66543663573103</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>65.13294714622531</v>
+        <v>45.61891418854885</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>75.98553334878349</v>
+        <v>51.61549255863508</v>
       </c>
     </row>
     <row r="11">
@@ -2612,17 +2612,17 @@
       <c r="B11" s="12" t="inlineStr"/>
       <c r="C11" s="12" t="inlineStr"/>
       <c r="D11" s="25" t="n">
-        <v>69.86792939869851</v>
+        <v>48.68117030863415</v>
       </c>
       <c r="E11" s="25" t="n">
-        <v>81.03635200364594</v>
+        <v>54.6354901142013</v>
       </c>
       <c r="F11" s="12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>※ 합산 P90은 회차별 충격이 독립이면 59.8억(분산효과 최대), 모든 회차가 함께 움직이면 69.9억이다. 실제 편성치는 그 사이이며, 연말 대량입금처럼 회차를 가로지르는 충격을 크게 볼수록 상단에 가깝다.</t>
+          <t>※ 합산 P90은 회차별 충격이 독립이면 42.7억(분산효과 최대), 모든 회차가 함께 움직이면 48.7억이다. 실제 편성치는 그 사이이며, 연말 대량입금처럼 회차를 가로지르는 충격을 크게 볼수록 상단에 가깝다.</t>
         </is>
       </c>
     </row>

--- a/reports/리워드유지_신청자·이전금액구간_스트레스테스트.xlsx
+++ b/reports/리워드유지_신청자·이전금액구간_스트레스테스트.xlsx
@@ -560,19 +560,19 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>20930</v>
+        <v>20162</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>9.382297070953255</v>
+        <v>9.03789710416793</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>37.08678701548362</v>
+        <v>35.72542655975362</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>3.952847232934134</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>13.77885918429242</v>
+        <v>13.27307274313385</v>
       </c>
     </row>
     <row r="6">
@@ -582,19 +582,19 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>26132</v>
+        <v>25306</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>11.71400283967624</v>
+        <v>11.34392603310242</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>46.30366371139683</v>
+        <v>44.84080663055841</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>3.952847232934134</v>
+        <v>3.952847232934135</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>17.23406105264504</v>
+        <v>16.68959078351905</v>
       </c>
     </row>
     <row r="7">
@@ -604,19 +604,19 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>26786</v>
+        <v>25914</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>12.00728069926224</v>
+        <v>11.61651810371527</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>47.46294628714218</v>
+        <v>45.9183214426002</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>3.952847232934135</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>17.66825007169669</v>
+        <v>17.09325799566292</v>
       </c>
     </row>
     <row r="8">
@@ -627,16 +627,16 @@
       </c>
       <c r="B8" s="8" t="inlineStr"/>
       <c r="C8" s="9" t="n">
-        <v>33.10358060989174</v>
+        <v>31.99834124098563</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>130.8533970140226</v>
+        <v>126.4845546329122</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>3.952847232934134</v>
+        <v>3.952847232934135</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>42.66543663573103</v>
+        <v>41.24616080233459</v>
       </c>
     </row>
     <row r="10">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>33.10358060989174</v>
+        <v>31.99834124098563</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>33.59569072772373</v>
+        <v>32.47260359142067</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>42.66543663573103</v>
+        <v>41.24616080233459</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>48.68117030863415</v>
+        <v>47.05592152231581</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>130.8533970140226</v>
+        <v>126.4845546329122</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>핵심: 리워드를 현재안대로 유지해도 신청자 1.8배 + 대량입금 믹스 상향이 겹치면 예산은 기준 대비 약 4.0배로 늘어난다. 편성 권고는 3회차 합 42.7~48.7억원(P90 범위).</t>
+          <t>핵심: 리워드를 현재안대로 유지해도 신청자 1.8배 + 대량입금 믹스 상향이 겹치면 예산은 기준 대비 약 4.0배로 늘어난다. 편성 권고는 3회차 합 41.2~47.1억원(P90 범위).</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>회차별 총 고객 수가 reference_deposit_events.csv 의 신청자수와 10건 중 9건 정확히 일치(1607 은 진행 경과로 16,356 → 17,399). 분포의 모집단이 '신청 고객'임이 확인된다</t>
+          <t>회차별 총 고객 수가 reference_deposit_events.csv 의 신청자수와 10건 중 9건 정확히 일치(1607 만 종료 직전 스냅샷 17,399 — 확정 17,496 대비 -0.6%). 분포의 모집단이 '신청 고객'임이 확인된다</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1902,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026_03  (기준 신청자 20,930명)</t>
+          <t>2026_03  (기준 신청자 20,162명)</t>
         </is>
       </c>
     </row>
@@ -1945,19 +1945,19 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>4.721311482271211</v>
+        <v>4.548004294768975</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>7.505837656762606</v>
+        <v>7.230317683334346</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>9.816069721665436</v>
+        <v>9.455747077803494</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>12.857601794226</v>
+        <v>12.38563233969023</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>16.48301645132605</v>
+        <v>15.8779673598905</v>
       </c>
     </row>
     <row r="6">
@@ -1967,19 +1967,19 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>5.311475417555115</v>
+        <v>5.116504831615098</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>8.444067363857931</v>
+        <v>8.134107393751137</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>11.04307843687361</v>
+        <v>10.63771546252893</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>14.46480201850425</v>
+        <v>13.93383638215151</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>18.54339350774181</v>
+        <v>17.86271327987681</v>
       </c>
     </row>
     <row r="7">
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B7" s="24" t="n">
-        <v>5.901639352839013</v>
+        <v>5.685005368461219</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>9.382297070953255</v>
+        <v>9.03789710416793</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>12.27008715208179</v>
+        <v>11.81968384725437</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>16.0720022427825</v>
+        <v>15.48204042461278</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>20.60377056415756</v>
+        <v>19.84745919986313</v>
       </c>
     </row>
     <row r="8">
@@ -2011,19 +2011,19 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>7.081967223406816</v>
+        <v>6.822006442153462</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>11.25875648514391</v>
+        <v>10.84547652500151</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>14.72410458249815</v>
+        <v>14.18362061670524</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>19.286402691339</v>
+        <v>18.57844850953534</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>24.72452467698908</v>
+        <v>23.81695103983575</v>
       </c>
     </row>
     <row r="9">
@@ -2033,19 +2033,19 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>8.852459029258522</v>
+        <v>8.527508052691829</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>14.07344560642988</v>
+        <v>13.55684565625189</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>18.40513072812269</v>
+        <v>17.72952577088155</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>24.10800336417375</v>
+        <v>23.22306063691918</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>30.90565584623634</v>
+        <v>29.77118879979469</v>
       </c>
     </row>
     <row r="10">
@@ -2055,32 +2055,32 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>10.62295083511023</v>
+        <v>10.2330096632302</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>16.88813472771586</v>
+        <v>16.26821478750227</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>22.08615687374722</v>
+        <v>21.27543092505787</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>28.92960403700851</v>
+        <v>27.86767276430302</v>
       </c>
       <c r="F10" s="25" t="n">
-        <v>37.08678701548362</v>
+        <v>35.72542655975362</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>기준셀 9.38억 → worst 37.09억 (×3.95) · 기준 당첨 4,167명</t>
+          <t>기준셀 9.04억 → worst 35.73억 (×3.95) · 기준 당첨 4,014명</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026_04  (기준 신청자 26,132명)</t>
+          <t>2026_04  (기준 신청자 25,306명)</t>
         </is>
       </c>
     </row>
@@ -2123,19 +2123,19 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>5.894660517789585</v>
+        <v>5.708432362468374</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>9.371202271740996</v>
+        <v>9.07514082648194</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>12.25557746940603</v>
+        <v>11.86839086593059</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>16.05299670112526</v>
+        <v>15.54583942650258</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>20.57940609395414</v>
+        <v>19.92924739135929</v>
       </c>
     </row>
     <row r="17">
@@ -2145,19 +2145,19 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>6.631493082513283</v>
+        <v>6.421986407776919</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>10.54260255570862</v>
+        <v>10.20953342979218</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>13.78752465308178</v>
+        <v>13.35193972417192</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>18.05962128876591</v>
+        <v>17.4890693548154</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>23.15183185569841</v>
+        <v>22.42040331527921</v>
       </c>
     </row>
     <row r="18">
@@ -2167,19 +2167,19 @@
         </is>
       </c>
       <c r="B18" s="24" t="n">
-        <v>7.368325647236983</v>
+        <v>7.135540453085467</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>11.71400283967624</v>
+        <v>11.34392603310242</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>15.31947183675753</v>
+        <v>14.83548858241324</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>20.06624587640656</v>
+        <v>19.43229928312822</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>25.72425761744269</v>
+        <v>24.91155923919911</v>
       </c>
     </row>
     <row r="19">
@@ -2189,19 +2189,19 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>8.841990776684378</v>
+        <v>8.562648543702558</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>14.05680340761149</v>
+        <v>13.61271123972291</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>18.38336620410904</v>
+        <v>17.80258629889589</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>24.07949505168788</v>
+        <v>23.31875913975387</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>30.86910914093122</v>
+        <v>29.89387108703893</v>
       </c>
     </row>
     <row r="20">
@@ -2211,19 +2211,19 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>11.05248847085547</v>
+        <v>10.7033106796282</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>17.57100425951436</v>
+        <v>17.01588904965364</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>22.9792077551363</v>
+        <v>22.25323287361986</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>30.09936881460985</v>
+        <v>29.14844892469234</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>38.58638642616402</v>
+        <v>37.36733885879867</v>
       </c>
     </row>
     <row r="21">
@@ -2233,32 +2233,32 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>13.26298616502657</v>
+        <v>12.84397281555384</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>21.08520511141724</v>
+        <v>20.41906685958436</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>27.57504930616356</v>
+        <v>26.70387944834383</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>36.11924257753182</v>
+        <v>34.9781387096308</v>
       </c>
       <c r="F21" s="25" t="n">
-        <v>46.30366371139683</v>
+        <v>44.84080663055841</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>기준셀 11.71억 → worst 46.30억 (×3.95) · 기준 당첨 5,202명</t>
+          <t>기준셀 11.34억 → worst 44.84억 (×3.95) · 기준 당첨 5,038명</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2027_01  (기준 신청자 26,786명)</t>
+          <t>2027_01  (기준 신청자 25,914명)</t>
         </is>
       </c>
     </row>
@@ -2301,19 +2301,19 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>6.0422423003198</v>
+        <v>5.845604748210128</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>9.605824559409793</v>
+        <v>9.293214482972219</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>12.56241447272684</v>
+        <v>12.15358571218982</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>16.45490786478835</v>
+        <v>15.91940256031704</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>21.09464279428541</v>
+        <v>20.40814286337786</v>
       </c>
     </row>
     <row r="28">
@@ -2323,19 +2323,19 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>6.797522587859775</v>
+        <v>6.576305341736394</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>10.80655262933601</v>
+        <v>10.45486629334375</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>14.1327162818177</v>
+        <v>13.67278392621355</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>18.51177134788689</v>
+        <v>17.90932788035667</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>23.73147314357109</v>
+        <v>22.9591607213001</v>
       </c>
     </row>
     <row r="29">
@@ -2345,19 +2345,19 @@
         </is>
       </c>
       <c r="B29" s="24" t="n">
-        <v>7.552802875399747</v>
+        <v>7.30700593526266</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>12.00728069926224</v>
+        <v>11.61651810371527</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>15.70301809090855</v>
+        <v>15.19198214023727</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>20.56863483098543</v>
+        <v>19.8992532003963</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>26.36830349285676</v>
+        <v>25.51017857922233</v>
       </c>
     </row>
     <row r="30">
@@ -2367,19 +2367,19 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>9.063363450479697</v>
+        <v>8.768407122315191</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>14.40873683911468</v>
+        <v>13.93982172445833</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>18.84362170909026</v>
+        <v>18.23037856828472</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>24.68236179718252</v>
+        <v>23.87910384047555</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>31.64196419142811</v>
+        <v>30.61221429506679</v>
       </c>
     </row>
     <row r="31">
@@ -2389,19 +2389,19 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>11.32920431309962</v>
+        <v>10.96050890289399</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>18.01092104889336</v>
+        <v>17.42477715557291</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>23.55452713636283</v>
+        <v>22.78797321035591</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>30.85295224647814</v>
+        <v>29.84887980059445</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>39.55245523928514</v>
+        <v>38.2652678688335</v>
       </c>
     </row>
     <row r="32">
@@ -2411,25 +2411,25 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>13.59504517571955</v>
+        <v>13.15261068347279</v>
       </c>
       <c r="C32" s="6" t="n">
-        <v>21.61310525867203</v>
+        <v>20.9097325866875</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>28.2654325636354</v>
+        <v>27.34556785242709</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>37.02354269577378</v>
+        <v>35.81865576071334</v>
       </c>
       <c r="F32" s="25" t="n">
-        <v>47.46294628714218</v>
+        <v>45.9183214426002</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>기준셀 12.01억 → worst 47.46억 (×3.95) · 기준 당첨 5,333명</t>
+          <t>기준셀 11.62억 → worst 45.92억 (×3.95) · 기준 당첨 5,159명</t>
         </is>
       </c>
     </row>
@@ -2522,19 +2522,19 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>9.671173972578575</v>
+        <v>9.316170078570266</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>9.198907181847725</v>
+        <v>8.861238985676682</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>13.77885918429242</v>
+        <v>13.27307274313385</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>15.46646483679792</v>
+        <v>14.89873073758991</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>19.06554148824232</v>
+        <v>18.36569455250382</v>
       </c>
     </row>
     <row r="8">
@@ -2544,19 +2544,19 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>12.09630222410399</v>
+        <v>11.71414755334655</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>11.52313235166203</v>
+        <v>11.15908565636958</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>17.23406105264504</v>
+        <v>16.68959078351905</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>19.30041578638071</v>
+        <v>18.69066382221197</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>23.6951316556239</v>
+        <v>22.94653881554381</v>
       </c>
     </row>
     <row r="9">
@@ -2566,19 +2566,19 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>12.41595426969426</v>
+        <v>12.01189188137046</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>11.78215123453676</v>
+        <v>11.39871520827502</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>17.66825007169669</v>
+        <v>17.09325799566292</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>19.86860949102268</v>
+        <v>19.22200934823613</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>24.76052284701722</v>
+        <v>23.95472123238562</v>
       </c>
     </row>
     <row r="10">
@@ -2588,19 +2588,19 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>34.18343046637683</v>
+        <v>33.04220951328728</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>33.59569072772373</v>
+        <v>32.47260359142067</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>42.66543663573103</v>
+        <v>41.24616080233459</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>45.61891418854885</v>
+        <v>44.10576216339236</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>51.61549255863508</v>
+        <v>49.88603733514756</v>
       </c>
     </row>
     <row r="11">
@@ -2612,17 +2612,17 @@
       <c r="B11" s="12" t="inlineStr"/>
       <c r="C11" s="12" t="inlineStr"/>
       <c r="D11" s="25" t="n">
-        <v>48.68117030863415</v>
+        <v>47.05592152231581</v>
       </c>
       <c r="E11" s="25" t="n">
-        <v>54.6354901142013</v>
+        <v>52.811403908038</v>
       </c>
       <c r="F11" s="12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>※ 합산 P90은 회차별 충격이 독립이면 42.7억(분산효과 최대), 모든 회차가 함께 움직이면 48.7억이다. 실제 편성치는 그 사이이며, 연말 대량입금처럼 회차를 가로지르는 충격을 크게 볼수록 상단에 가깝다.</t>
+          <t>※ 합산 P90은 회차별 충격이 독립이면 41.2억(분산효과 최대), 모든 회차가 함께 움직이면 47.1억이다. 실제 편성치는 그 사이이며, 연말 대량입금처럼 회차를 가로지르는 충격을 크게 볼수록 상단에 가깝다.</t>
         </is>
       </c>
     </row>
@@ -2718,19 +2718,19 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>20930</v>
+        <v>20162</v>
       </c>
       <c r="D4" s="17" t="n">
         <v>0.1990845309720363</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>4167</v>
+        <v>4014</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>225162</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>9.382297070953255</v>
+        <v>9.03789710416793</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>1</v>
@@ -2748,19 +2748,19 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>37675</v>
+        <v>36292</v>
       </c>
       <c r="D5" s="17" t="n">
         <v>0.1990845309720363</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>7500</v>
+        <v>7225</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>225162</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>16.88813472771586</v>
+        <v>16.26821478750227</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>1.8</v>
@@ -2778,22 +2778,22 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>20930</v>
+        <v>20162</v>
       </c>
       <c r="D6" s="17" t="n">
         <v>0.392222908756043</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>8209</v>
+        <v>7908</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>250979</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>20.60377056415756</v>
+        <v>19.84745919986313</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>2.196026240518963</v>
+        <v>2.196026240518964</v>
       </c>
     </row>
     <row r="7">
@@ -2808,19 +2808,19 @@
         </is>
       </c>
       <c r="C7" s="20" t="n">
-        <v>37675</v>
+        <v>36292</v>
       </c>
       <c r="D7" s="19" t="n">
         <v>0.392222908756043</v>
       </c>
       <c r="E7" s="20" t="n">
-        <v>14777</v>
+        <v>14234</v>
       </c>
       <c r="F7" s="20" t="n">
         <v>250979</v>
       </c>
       <c r="G7" s="25" t="n">
-        <v>37.08678701548362</v>
+        <v>35.72542655975362</v>
       </c>
       <c r="H7" s="21" t="n">
         <v>3.952847232934134</v>
@@ -2838,19 +2838,19 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>26132</v>
+        <v>25306</v>
       </c>
       <c r="D9" s="17" t="n">
         <v>0.1990845309720363</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>5202</v>
+        <v>5038</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>225162</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>11.71400283967624</v>
+        <v>11.34392603310242</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>1</v>
@@ -2868,19 +2868,19 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>47038</v>
+        <v>45551</v>
       </c>
       <c r="D10" s="17" t="n">
         <v>0.1990845309720363</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>9364</v>
+        <v>9069</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>225162</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>21.08520511141724</v>
+        <v>20.41906685958436</v>
       </c>
       <c r="H10" s="7" t="n">
         <v>1.8</v>
@@ -2898,19 +2898,19 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>26132</v>
+        <v>25306</v>
       </c>
       <c r="D11" s="17" t="n">
         <v>0.392222908756043</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>10250</v>
+        <v>9926</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>250979</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>25.72425761744269</v>
+        <v>24.91155923919911</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>2.196026240518963</v>
@@ -2928,22 +2928,22 @@
         </is>
       </c>
       <c r="C12" s="20" t="n">
-        <v>47038</v>
+        <v>45551</v>
       </c>
       <c r="D12" s="19" t="n">
         <v>0.392222908756043</v>
       </c>
       <c r="E12" s="20" t="n">
-        <v>18449</v>
+        <v>17866</v>
       </c>
       <c r="F12" s="20" t="n">
         <v>250979</v>
       </c>
       <c r="G12" s="25" t="n">
-        <v>46.30366371139683</v>
+        <v>44.84080663055841</v>
       </c>
       <c r="H12" s="21" t="n">
-        <v>3.952847232934134</v>
+        <v>3.952847232934135</v>
       </c>
     </row>
     <row r="14">
@@ -2958,19 +2958,19 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>26786</v>
+        <v>25914</v>
       </c>
       <c r="D14" s="17" t="n">
         <v>0.1990845309720363</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>5333</v>
+        <v>5159</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>225162</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>12.00728069926224</v>
+        <v>11.61651810371527</v>
       </c>
       <c r="H14" s="7" t="n">
         <v>1</v>
@@ -2988,19 +2988,19 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>48215</v>
+        <v>46646</v>
       </c>
       <c r="D15" s="17" t="n">
         <v>0.1990845309720363</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>9599</v>
+        <v>9287</v>
       </c>
       <c r="F15" s="5" t="n">
         <v>225162</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>21.61310525867203</v>
+        <v>20.9097325866875</v>
       </c>
       <c r="H15" s="7" t="n">
         <v>1.8</v>
@@ -3018,22 +3018,22 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>26786</v>
+        <v>25914</v>
       </c>
       <c r="D16" s="17" t="n">
         <v>0.392222908756043</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>10506</v>
+        <v>10164</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>250979</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>26.36830349285676</v>
+        <v>25.51017857922233</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>2.196026240518963</v>
+        <v>2.196026240518964</v>
       </c>
     </row>
     <row r="17">
@@ -3048,19 +3048,19 @@
         </is>
       </c>
       <c r="C17" s="20" t="n">
-        <v>48215</v>
+        <v>46646</v>
       </c>
       <c r="D17" s="19" t="n">
         <v>0.392222908756043</v>
       </c>
       <c r="E17" s="20" t="n">
-        <v>18911</v>
+        <v>18296</v>
       </c>
       <c r="F17" s="20" t="n">
         <v>250979</v>
       </c>
       <c r="G17" s="25" t="n">
-        <v>47.46294628714218</v>
+        <v>45.9183214426002</v>
       </c>
       <c r="H17" s="21" t="n">
         <v>3.952847232934135</v>
